--- a/src/attributions/attributions_saliency_traj_491.xlsx
+++ b/src/attributions/attributions_saliency_traj_491.xlsx
@@ -999,4554 +999,4554 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0006184637313708663</v>
+        <v>0.00970968883484602</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00476343184709549</v>
+        <v>0.0451798103749752</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004146610735915601</v>
+        <v>0.01348309684544802</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008941190899349749</v>
+        <v>0.02295456826686859</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002203565556555986</v>
+        <v>0.02370870299637318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000329216243699193</v>
+        <v>0.0216064378619194</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001714719692245126</v>
+        <v>0.003695936873555183</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003311063919682056</v>
+        <v>3.329195897094905e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006215803441591561</v>
+        <v>0.002426257822662592</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003730700991582125</v>
+        <v>0.01627648621797562</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004438105039298534</v>
+        <v>0.05554525554180145</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001182773194159381</v>
+        <v>0.01938305236399174</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001414765371009707</v>
+        <v>0.0354086235165596</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002428240841254592</v>
+        <v>0.03286122158169746</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005920988041907549</v>
+        <v>0.01382856443524361</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001112626923713833</v>
+        <v>0.0003154263831675053</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007577817887067795</v>
+        <v>0.004256656859070063</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001360984751954675</v>
+        <v>0.004789714235812426</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004709229688160121</v>
+        <v>0.003468303009867668</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000754053529817611</v>
+        <v>0.01209551189094782</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006423523300327361</v>
+        <v>0.003705662209540606</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002372158196521923</v>
+        <v>0.0008957773097790778</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001034643151797354</v>
+        <v>0.001415984472259879</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0005914486246183515</v>
+        <v>0.001466318499296904</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0004915328463539481</v>
+        <v>0.002301702741533518</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0001590716710779816</v>
+        <v>0.001564726349897683</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0005773656303063035</v>
+        <v>0.005191678646951914</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001114204642362893</v>
+        <v>0.003031260333955288</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.884226316586137e-06</v>
+        <v>0.0100356712937355</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0007606126600876451</v>
+        <v>0.004526362754404545</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0002388908615102991</v>
+        <v>0.0003064924385398626</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0004492599400691688</v>
+        <v>0.01270303316414356</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0001453506120014936</v>
+        <v>0.00183723762165755</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0003812822396866977</v>
+        <v>0.003336774185299873</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.801933442242444e-05</v>
+        <v>0.001049594953656197</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0002257270243717358</v>
+        <v>0.002157746348530054</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.000494409934617579</v>
+        <v>0.001527308253571391</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0004363297775853425</v>
+        <v>0.007662929594516754</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0003896235721185803</v>
+        <v>0.004810727201402187</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.592168261297047e-05</v>
+        <v>0.003406894393265247</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0004696812247857451</v>
+        <v>0.006508902180939913</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0002634513657540083</v>
+        <v>0.005922614596784115</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0001434878795407712</v>
+        <v>0.0002985763130709529</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.726413943804801e-05</v>
+        <v>0.0001809728710213676</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0002160621515940875</v>
+        <v>2.582019078545272e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0006204246310517192</v>
+        <v>0.001583276549354196</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.003544360864907503</v>
+        <v>0.03667453676462173</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0009590242989361286</v>
+        <v>0.001648971694521606</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0004382229817565531</v>
+        <v>0.01131606660783291</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0002601140004117042</v>
+        <v>0.007216588594019413</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.00111498567275703</v>
+        <v>0.003279511351138353</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0005110308993607759</v>
+        <v>0.001092583173885942</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0002412261965218931</v>
+        <v>0.00256677670404315</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0002735862508416176</v>
+        <v>0.002542776754125953</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0006004564929753542</v>
+        <v>0.001129744458012283</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0005661030299961567</v>
+        <v>0.002978315344080329</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.001025664852932096</v>
+        <v>0.009776165708899498</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0001167943773907609</v>
+        <v>0.003975817002356052</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.001659724395722151</v>
+        <v>0.007264295127242804</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0005609479267150164</v>
+        <v>0.008493676781654358</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0001409795368090272</v>
+        <v>0.001598338247276843</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.000484552641864866</v>
+        <v>0.00360548566095531</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0001780775928637013</v>
+        <v>0.002991281682625413</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0006287094438448548</v>
+        <v>0.004322553053498268</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0006116490112617612</v>
+        <v>0.001975116087123752</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0001836331939557567</v>
+        <v>0.008483322337269783</v>
       </c>
       <c r="BO2" t="n">
-        <v>7.840314356144518e-05</v>
+        <v>0.003953872248530388</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0002172122185584158</v>
+        <v>0.01454993523657322</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0005608773208223283</v>
+        <v>0.006510255858302116</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0001992060133488849</v>
+        <v>0.003321542870253325</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0001780190214049071</v>
+        <v>0.003269510343670845</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0004929237184114754</v>
+        <v>0.0002632435935083777</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0001998037478188053</v>
+        <v>0.005428747273981571</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.002019378356635571</v>
+        <v>0.01595204323530197</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.000196588400285691</v>
+        <v>0.0004460026975721121</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0002002307592192665</v>
+        <v>0.00773073174059391</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0007421814952977002</v>
+        <v>0.003090834245085716</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0005055477377027273</v>
+        <v>0.003177286591380835</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.328689389396459e-05</v>
+        <v>0.001779519603587687</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0001402376219630241</v>
+        <v>0.0007399222813546658</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.144872607663274e-06</v>
+        <v>0.001283986028283834</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0002519027329981327</v>
+        <v>0.002008565003052354</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0007227173773571849</v>
+        <v>0.0125410296022892</v>
       </c>
       <c r="CF2" t="n">
-        <v>8.077397797023878e-05</v>
+        <v>0.007011932320892811</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0001540024532005191</v>
+        <v>0.004189349710941315</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0001075305990525521</v>
+        <v>0.002950404305011034</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0001242550060851499</v>
+        <v>0.003869120497256517</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0002408526925137267</v>
+        <v>0.0003075789427384734</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0001017292306642048</v>
+        <v>0.001345774158835411</v>
       </c>
       <c r="CL2" t="n">
-        <v>7.478615589207038e-05</v>
+        <v>0.0006806150777265429</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.0009851963259279728</v>
+        <v>0.0008248146623373032</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0006910686497576535</v>
+        <v>0.01432758569717407</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0001202819184982218</v>
+        <v>0.006571692880243063</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0002148928761016577</v>
+        <v>0.0003843222511932254</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.00145762728061527</v>
+        <v>0.006901936139911413</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.001130081596784294</v>
+        <v>0.0005509769544005394</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0005575827672146261</v>
+        <v>0.00426776148378849</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.000866304209921509</v>
+        <v>0.0004654957447201014</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0003177698235958815</v>
+        <v>0.003308812156319618</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0001957984350156039</v>
+        <v>0.004085459746420383</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0007622389239259064</v>
+        <v>0.0136700551956892</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0001124759437516332</v>
+        <v>0.005764019209891558</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0002649619127623737</v>
+        <v>0.005995688028633595</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.843650509021245e-05</v>
+        <v>0.004801333416253328</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.000195275541045703</v>
+        <v>0.005724246613681316</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0001868744730018079</v>
+        <v>0.0002020535175688565</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0001259532291442156</v>
+        <v>0.0006107855588197708</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.263063652208075e-05</v>
+        <v>0.00165164889767766</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0002129757485818118</v>
+        <v>0.008537525311112404</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0005583444726653397</v>
+        <v>0.01474347524344921</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0003899338480550796</v>
+        <v>0.01166252698749304</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.001612175488844514</v>
+        <v>0.01163377054035664</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.001641806913539767</v>
+        <v>0.01700906828045845</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0001784724881872535</v>
+        <v>0.01251191552728415</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.0003033822576981038</v>
+        <v>0.00410568667575717</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.0003771347401198</v>
+        <v>0.006937039084732533</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0002759488997980952</v>
+        <v>0.0008432118338532746</v>
       </c>
       <c r="DN2" t="n">
-        <v>9.103197953663766e-06</v>
+        <v>0.002669035922735929</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0008605067268945277</v>
+        <v>0.01384820975363255</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.0006332428310997784</v>
+        <v>0.008167448453605175</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0002462833654135466</v>
+        <v>0.0006840265705250204</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0004635195073205978</v>
+        <v>0.006735417060554028</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0003190543211530894</v>
+        <v>0.01693317294120789</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0004816080327145755</v>
+        <v>0.0005423862021416426</v>
       </c>
       <c r="DU2" t="n">
-        <v>2.782748197205365e-06</v>
+        <v>0.00145328463986516</v>
       </c>
       <c r="DV2" t="n">
-        <v>2.101414793287404e-05</v>
+        <v>0.003711295779794455</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0004714967799372971</v>
+        <v>0.003974920138716698</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0004510220605880022</v>
+        <v>0.004812492057681084</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0005265235668048263</v>
+        <v>0.000912673189304769</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0004873221332672983</v>
+        <v>0.0006487861974164844</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0001385943323839456</v>
+        <v>0.000787213328294456</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0006394952652044594</v>
+        <v>0.005087509751319885</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.0001288783096242696</v>
+        <v>0.002254416234791279</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0004032015567645431</v>
+        <v>0.007881049066781998</v>
       </c>
       <c r="EE2" t="n">
-        <v>8.118333062157035e-05</v>
+        <v>0.006281148176640272</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0002009267918765545</v>
+        <v>0.003513649106025696</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0009082063334062696</v>
+        <v>0.01212956942617893</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0001120276720030233</v>
+        <v>0.0001819374156184494</v>
       </c>
       <c r="EI2" t="n">
-        <v>4.667410757974721e-05</v>
+        <v>0.004913544282317162</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.000688649364747107</v>
+        <v>0.002080828417092562</v>
       </c>
       <c r="EK2" t="n">
-        <v>1.156340294983238e-05</v>
+        <v>0.006255416199564934</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.000169338847626932</v>
+        <v>0.00025183692923747</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0002326948597328737</v>
+        <v>0.0004691840149462223</v>
       </c>
       <c r="EN2" t="n">
-        <v>9.615978342480958e-07</v>
+        <v>0.000221267924644053</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0004128953150939196</v>
+        <v>0.003765553701668978</v>
       </c>
       <c r="EP2" t="n">
-        <v>9.475857950747013e-06</v>
+        <v>0.0007107648998498917</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.0006554437568411231</v>
+        <v>0.003630495397374034</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0001724142202874646</v>
+        <v>0.002388957887887955</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0001803767227102071</v>
+        <v>0.006805984303355217</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.0004228504258207977</v>
+        <v>0.00683670025318861</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.0003771490009967238</v>
+        <v>0.002172898733988404</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0003711172030307353</v>
+        <v>0.002302395412698388</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.0004033531295135617</v>
+        <v>0.001323018572293222</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0003136066370643675</v>
+        <v>0.00136877759359777</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.0007326945196837187</v>
+        <v>0.01517295837402344</v>
       </c>
       <c r="EZ2" t="n">
-        <v>7.370737148448825e-05</v>
+        <v>0.003856466617435217</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0001572491164552048</v>
+        <v>0.005077840760350227</v>
       </c>
       <c r="FB2" t="n">
-        <v>7.118254143279046e-05</v>
+        <v>0.003160046646371484</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0001196583762066439</v>
+        <v>0.003546237945556641</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0001649462792556733</v>
+        <v>0.0005344891687855124</v>
       </c>
       <c r="FE2" t="n">
-        <v>9.199728083331138e-05</v>
+        <v>0.0002473680069670081</v>
       </c>
       <c r="FF2" t="n">
-        <v>9.179377229884267e-06</v>
+        <v>0.0007300936267711222</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0001401844201609492</v>
+        <v>0.00154630932956934</v>
       </c>
       <c r="FH2" t="n">
-        <v>6.568060780409724e-05</v>
+        <v>0.006504431366920471</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0001031939027598128</v>
+        <v>0.003790399292483926</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0002707848616410047</v>
+        <v>0.008343224413692951</v>
       </c>
       <c r="FK2" t="n">
-        <v>8.647446520626545e-05</v>
+        <v>0.003660253714770079</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.000283149944152683</v>
+        <v>0.002256078878417611</v>
       </c>
       <c r="FM2" t="n">
-        <v>3.676629421534017e-05</v>
+        <v>0.0008164478931576014</v>
       </c>
       <c r="FN2" t="n">
-        <v>5.364536627894267e-05</v>
+        <v>0.004367479123175144</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0003997340390924364</v>
+        <v>0.003138814819976687</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0004145541752222925</v>
+        <v>0.004151391331106424</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0006704287370666862</v>
+        <v>0.01583016291260719</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.0004087214183527976</v>
+        <v>0.01352288480848074</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.001354092732071877</v>
+        <v>0.02136798575520515</v>
       </c>
       <c r="FT2" t="n">
-        <v>5.720392800867558e-05</v>
+        <v>0.01303346641361713</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0001662523136474192</v>
+        <v>0.007814712822437286</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.0001713136734906584</v>
+        <v>0.002955809235572815</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0005310161504894495</v>
+        <v>0.002712293993681669</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0002395737974438816</v>
+        <v>0.007036582101136446</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0004987249267287552</v>
+        <v>0.005813300609588623</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.0003098983142990619</v>
+        <v>0.0123095391318202</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0004971420858055353</v>
+        <v>0.007793235592544079</v>
       </c>
       <c r="GB2" t="n">
-        <v>5.407750722952187e-05</v>
+        <v>0.003952337428927422</v>
       </c>
       <c r="GC2" t="n">
-        <v>3.082613693550229e-05</v>
+        <v>0.01621723361313343</v>
       </c>
       <c r="GD2" t="n">
-        <v>8.103522850433365e-05</v>
+        <v>0.001555991591885686</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0003232285962440073</v>
+        <v>0.007541499100625515</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0001245772000402212</v>
+        <v>0.002741019474342465</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.000520662812050432</v>
+        <v>0.0009499863954260945</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01152936182916164</v>
+        <v>0.2087545990943909</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1782610267400742</v>
+        <v>0.4851995706558228</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01226014457643032</v>
+        <v>0.09901180863380432</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02961834147572517</v>
+        <v>0.08221966028213501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03137382119894028</v>
+        <v>0.2026634961366653</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006352984812110662</v>
+        <v>0.1128839552402496</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01430722419172525</v>
+        <v>0.3945290148258209</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02908978797495365</v>
+        <v>0.2210572957992554</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1298351883888245</v>
+        <v>1.201029062271118</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01617675647139549</v>
+        <v>0.1349977254867554</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07944029569625854</v>
+        <v>0.682358980178833</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008979825302958488</v>
+        <v>0.1717721521854401</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04659069329500198</v>
+        <v>0.07382381707429886</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04798867553472519</v>
+        <v>0.4118669331073761</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03530345484614372</v>
+        <v>0.03097625076770782</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05533398687839508</v>
+        <v>0.5205425620079041</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002910885959863663</v>
+        <v>0.08269132673740387</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08632022142410278</v>
+        <v>0.9281104803085327</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01816916093230247</v>
+        <v>0.03904929757118225</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009348210878670216</v>
+        <v>0.06935210525989532</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01102938409894705</v>
+        <v>0.02018002048134804</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02365856245160103</v>
+        <v>0.3624728620052338</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03907852992415428</v>
+        <v>0.4094346463680267</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01283884979784489</v>
+        <v>0.3410029411315918</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009419890120625496</v>
+        <v>0.143648698925972</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0006275337655097246</v>
+        <v>0.05864014104008675</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02134400978684425</v>
+        <v>0.4388938248157501</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006210088729858398</v>
+        <v>0.03097546845674515</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03700423985719681</v>
+        <v>0.2083461880683899</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02261385135352612</v>
+        <v>0.1166436523199081</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.02985256165266037</v>
+        <v>0.4244943559169769</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.03087764047086239</v>
+        <v>0.17135289311409</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002271047327667475</v>
+        <v>0.1916670501232147</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02632281556725502</v>
+        <v>0.2381042838096619</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.03706740960478783</v>
+        <v>0.4495856165885925</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.04280542582273483</v>
+        <v>0.2350030243396759</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01079040300101042</v>
+        <v>0.1075781509280205</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.002759372582659125</v>
+        <v>0.0349092073738575</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.02546924352645874</v>
+        <v>0.1396134048700333</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.01802827976644039</v>
+        <v>0.09347830712795258</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.01301197428256273</v>
+        <v>0.06075935810804367</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001994511112570763</v>
+        <v>0.0644402951002121</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.05125737562775612</v>
+        <v>0.03317815065383911</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.03917129337787628</v>
+        <v>0.1527702957391739</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.01773912459611893</v>
+        <v>0.2027265876531601</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.03379661589860916</v>
+        <v>0.09816870093345642</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1353822946548462</v>
+        <v>0.4887141287326813</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.03081445768475533</v>
+        <v>0.08758866041898727</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.04799190163612366</v>
+        <v>0.1548880785703659</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.09658300131559372</v>
+        <v>0.1554781049489975</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.003006234765052795</v>
+        <v>0.0704621896147728</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.06859251856803894</v>
+        <v>0.09912175685167313</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.006544290110468864</v>
+        <v>0.06160171702504158</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.07342606037855148</v>
+        <v>0.5585058927536011</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.006298691965639591</v>
+        <v>0.05206391587853432</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01758423447608948</v>
+        <v>0.03002547845244408</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.008242582902312279</v>
+        <v>0.05782674252986908</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.002647412940859795</v>
+        <v>0.2817713022232056</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.02855051681399345</v>
+        <v>0.2741562724113464</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.01079356390982866</v>
+        <v>0.2479980885982513</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.004512272775173187</v>
+        <v>0.2095350623130798</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.04885713011026382</v>
+        <v>0.4753175973892212</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.03032658062875271</v>
+        <v>0.2778063714504242</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.001340679824352264</v>
+        <v>0.05159127712249756</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.01262510195374489</v>
+        <v>0.1595407575368881</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.03344648331403732</v>
+        <v>0.06467947363853455</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0387890562415123</v>
+        <v>0.002950906753540039</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.07151728868484497</v>
+        <v>0.1736003458499908</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0156768225133419</v>
+        <v>0.002531457925215364</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.003452407196164131</v>
+        <v>0.22927026450634</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.01952525228261948</v>
+        <v>0.1335314959287643</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0238211452960968</v>
+        <v>0.2847023010253906</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.009298563003540039</v>
+        <v>0.080078125</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.05166167020797729</v>
+        <v>0.1138344407081604</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.01036408729851246</v>
+        <v>0.04401735588908195</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.04711204767227173</v>
+        <v>0.3045783042907715</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.01049862429499626</v>
+        <v>0.4895129799842834</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.004462867043912411</v>
+        <v>0.2289839833974838</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.02590188756585121</v>
+        <v>0.2132586687803268</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.01067181397229433</v>
+        <v>0.3087752461433411</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.02659551426768303</v>
+        <v>0.7514644265174866</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.005014932714402676</v>
+        <v>0.04547552019357681</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.03099340572953224</v>
+        <v>0.1096192076802254</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.001061635557562113</v>
+        <v>0.0221431590616703</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.004761809948831797</v>
+        <v>0.1535420119762421</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002555821847636253</v>
+        <v>0.04623211547732353</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01227218750864267</v>
+        <v>0.01940003782510757</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.004261107183992863</v>
+        <v>0.03310709074139595</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.005375828593969345</v>
+        <v>0.09747607260942459</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.02677060663700104</v>
+        <v>0.2707391679286957</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.00290565611794591</v>
+        <v>0.02980310097336769</v>
       </c>
       <c r="CN3" t="n">
-        <v>6.523309275507927e-05</v>
+        <v>0.2506648004055023</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.00116512062959373</v>
+        <v>0.07856414467096329</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.06591906398534775</v>
+        <v>0.2378589510917664</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0293529350310564</v>
+        <v>0.1761960536241531</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.03952721506357193</v>
+        <v>0.3680673837661743</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.06638714671134949</v>
+        <v>0.2540380656719208</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.05186416953802109</v>
+        <v>0.06000420078635216</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.02429236099123955</v>
+        <v>0.3067188262939453</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.002572345547378063</v>
+        <v>0.02954771742224693</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03703708946704865</v>
+        <v>0.1157954409718513</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.006408960558474064</v>
+        <v>0.005473105236887932</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.00948619470000267</v>
+        <v>0.1437094956636429</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.003297979943454266</v>
+        <v>0.008549276739358902</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01087930984795094</v>
+        <v>0.07500159740447998</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.004451658576726913</v>
+        <v>0.0482671745121479</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.003889592364430428</v>
+        <v>0.02212381921708584</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.01688067615032196</v>
+        <v>0.2769249677658081</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0283379927277565</v>
+        <v>0.02642064914107323</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1393545120954514</v>
+        <v>0.3493929803371429</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.04870481789112091</v>
+        <v>0.09686505049467087</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.01484349370002747</v>
+        <v>0.1990238428115845</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0341915637254715</v>
+        <v>0.5437232851982117</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1558210104703903</v>
+        <v>0.09087376296520233</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.04352688789367676</v>
+        <v>0.03443238511681557</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0724974051117897</v>
+        <v>0.3886468708515167</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.01410841289907694</v>
+        <v>0.2035156637430191</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.006652312353253365</v>
+        <v>0.02883232198655605</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.02121231146156788</v>
+        <v>0.08697112649679184</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.009005764499306679</v>
+        <v>0.1321179419755936</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.01735039427876472</v>
+        <v>0.09251613914966583</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.006063998211175203</v>
+        <v>0.06008497253060341</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.01673272997140884</v>
+        <v>0.2033773958683014</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06137889623641968</v>
+        <v>0.4036879241466522</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.01309160515666008</v>
+        <v>0.03661855310201645</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.01230789162218571</v>
+        <v>0.03323844447731972</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.006441265344619751</v>
+        <v>0.04953720420598984</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.03135216981172562</v>
+        <v>0.1720291376113892</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.008300123736262321</v>
+        <v>0.09083228558301926</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.02461468428373337</v>
+        <v>0.04498973116278648</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.005940431728959084</v>
+        <v>0.2439519762992859</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.008487161248922348</v>
+        <v>0.07955282181501389</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.02660967409610748</v>
+        <v>0.1933657675981522</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.01171810831874609</v>
+        <v>0.2326314747333527</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.007438339293003082</v>
+        <v>0.06871576607227325</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01032709330320358</v>
+        <v>0.09038180112838745</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.001015158370137215</v>
+        <v>0.04538474977016449</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.01768751814961433</v>
+        <v>0.001247746171429753</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.02220187336206436</v>
+        <v>0.06586708873510361</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.007032772991806269</v>
+        <v>0.06313934922218323</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.05773446336388588</v>
+        <v>0.008513558655977249</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.01156523823738098</v>
+        <v>0.1252472698688507</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.005440158303827047</v>
+        <v>0.06013659760355949</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.03067075274884701</v>
+        <v>0.2601230442523956</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.02112692594528198</v>
+        <v>0.01992340572178364</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.03133057430386543</v>
+        <v>0.19394651055336</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.04367277026176453</v>
+        <v>0.01899318397045135</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.00346369668841362</v>
+        <v>0.09290864318609238</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.006420149002224207</v>
+        <v>0.01594166830182076</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.03349399566650391</v>
+        <v>0.1386958062648773</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.01125721633434296</v>
+        <v>0.08258450031280518</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.029476223513484</v>
+        <v>0.03035328350961208</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.004354333039373159</v>
+        <v>0.1319904625415802</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.004308970179408789</v>
+        <v>0.05952536314725876</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0384598895907402</v>
+        <v>0.1569063663482666</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.00241465400904417</v>
+        <v>0.01085709035396576</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01019707508385181</v>
+        <v>0.1346352696418762</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01056466810405254</v>
+        <v>0.05876806378364563</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.0006864918395876884</v>
+        <v>0.04563707485795021</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.01061204634606838</v>
+        <v>0.0909857451915741</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.005093319341540337</v>
+        <v>0.0866934210062027</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.007185996510088444</v>
+        <v>0.2916267514228821</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01893564686179161</v>
+        <v>0.006745539605617523</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.02247143350541592</v>
+        <v>0.2027453184127808</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03111354447901249</v>
+        <v>0.01461035944521427</v>
       </c>
       <c r="FJ3" t="n">
-        <v>9.989086538553238e-05</v>
+        <v>0.1962979435920715</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.02828460559248924</v>
+        <v>0.06961172819137573</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.0139035452157259</v>
+        <v>0.2054396122694016</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.03155818581581116</v>
+        <v>0.4781634211540222</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.005348025821149349</v>
+        <v>0.007012560963630676</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.00641926983371377</v>
+        <v>0.2867870926856995</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.003497234312817454</v>
+        <v>0.1393172144889832</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.01387394964694977</v>
+        <v>0.1435003727674484</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.02588509954512119</v>
+        <v>0.2874521911144257</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.03315547853708267</v>
+        <v>0.6063867211341858</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.03249889239668846</v>
+        <v>0.8523182272911072</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.01056289207190275</v>
+        <v>0.2808652520179749</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.03609571605920792</v>
+        <v>0.1978455036878586</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.01102140359580517</v>
+        <v>0.06988650560379028</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.01355948578566313</v>
+        <v>0.5297003388404846</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.0007105967961251736</v>
+        <v>0.07781723141670227</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.02934798039495945</v>
+        <v>0.08227717876434326</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.003699176479130983</v>
+        <v>0.03085917048156261</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.03079827874898911</v>
+        <v>0.2800693809986115</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.05370104685425758</v>
+        <v>0.1273536831140518</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.03623992204666138</v>
+        <v>0.01125921308994293</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.003669572062790394</v>
+        <v>0.1380627900362015</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.04842251166701317</v>
+        <v>0.381206601858139</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.03400640934705734</v>
+        <v>0.4259591698646545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.003361478447914124</v>
+        <v>0.2020082622766495</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7507198452949524</v>
+        <v>0.6366406679153442</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07922834157943726</v>
+        <v>0.2405601739883423</v>
       </c>
       <c r="D4" t="n">
-        <v>0.314172625541687</v>
+        <v>0.04195435345172882</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1338299512863159</v>
+        <v>0.1129437759518623</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5305429697036743</v>
+        <v>0.489133358001709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03045472502708435</v>
+        <v>0.06341937184333801</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2506428360939026</v>
+        <v>0.1577872335910797</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007573760114610195</v>
+        <v>0.06868238002061844</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08205021917819977</v>
+        <v>0.1297592520713806</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6490733623504639</v>
+        <v>0.659105122089386</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01116014644503593</v>
+        <v>0.3059167861938477</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3109753727912903</v>
+        <v>0.1493519693613052</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05633020028471947</v>
+        <v>0.05368497595191002</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5238449573516846</v>
+        <v>0.3870744109153748</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04135657474398613</v>
+        <v>0.0528068020939827</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08660420030355453</v>
+        <v>0.146883100271225</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05926688760519028</v>
+        <v>0.1603998839855194</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01781830191612244</v>
+        <v>0.002543600276112556</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02810460329055786</v>
+        <v>0.1396566927433014</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002812668681144714</v>
+        <v>0.07930494099855423</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1197634413838387</v>
+        <v>0.09534667432308197</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05969976633787155</v>
+        <v>0.08059285581111908</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0007058726623654366</v>
+        <v>0.0003476813435554504</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.009603707119822502</v>
+        <v>0.01531552895903587</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007512208074331284</v>
+        <v>0.02317275106906891</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04209364578127861</v>
+        <v>0.0662209689617157</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02216597087681293</v>
+        <v>0.1064585149288177</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.03416857868432999</v>
+        <v>0.0616704486310482</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.03427781164646149</v>
+        <v>0.1017654538154602</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01790502108633518</v>
+        <v>0.233674556016922</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.08096911013126373</v>
+        <v>0.02767910808324814</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.006937074474990368</v>
+        <v>0.06221821159124374</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03411012142896652</v>
+        <v>0.00184500589966774</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.05701792985200882</v>
+        <v>0.04613860324025154</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1105770021677017</v>
+        <v>0.02493216842412949</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02352166920900345</v>
+        <v>0.07525254786014557</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1089097633957863</v>
+        <v>0.1143577545881271</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001316145062446594</v>
+        <v>0.0130716860294342</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.03339801356196404</v>
+        <v>0.08544526994228363</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.09145805984735489</v>
+        <v>0.1382392793893814</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1290148943662643</v>
+        <v>0.02454528398811817</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.01876232773065567</v>
+        <v>0.01773821748793125</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.06726065278053284</v>
+        <v>0.02352855540812016</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0897795706987381</v>
+        <v>0.005421509500592947</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.09464669227600098</v>
+        <v>0.1228415593504906</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4950433373451233</v>
+        <v>0.3997474908828735</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.01975326985120773</v>
+        <v>0.1101590991020203</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.08749280869960785</v>
+        <v>0.1081507802009583</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.08270718157291412</v>
+        <v>0.07932403683662415</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1589120328426361</v>
+        <v>0.07990659773349762</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02672669105231762</v>
+        <v>0.03993324935436249</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1253669261932373</v>
+        <v>0.01676351763308048</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.07655183225870132</v>
+        <v>0.06266258656978607</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.03353795781731606</v>
+        <v>0.07689314335584641</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.2099283337593079</v>
+        <v>0.0966358408331871</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1455328911542892</v>
+        <v>0.08654305338859558</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1139427870512009</v>
+        <v>0.04711204022169113</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.09370386600494385</v>
+        <v>0.05072108283638954</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.2270079702138901</v>
+        <v>0.1501335501670837</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0007373690605163574</v>
+        <v>0.03834988921880722</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.07845194637775421</v>
+        <v>0.05685589835047722</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.09560799598693848</v>
+        <v>0.008872546255588531</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0281764343380928</v>
+        <v>0.03915917500853539</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.08517435193061829</v>
+        <v>0.06563529372215271</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.03907392546534538</v>
+        <v>0.08601298183202744</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.02959974482655525</v>
+        <v>0.07663790136575699</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.04077870771288872</v>
+        <v>0.01686411909759045</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.03837387263774872</v>
+        <v>0.05874060094356537</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.07436995953321457</v>
+        <v>0.1442919373512268</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.02294033765792847</v>
+        <v>0.03868710994720459</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.02937939763069153</v>
+        <v>0.09554463624954224</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.05226405337452888</v>
+        <v>0.06892094016075134</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2364303171634674</v>
+        <v>0.2616062462329865</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.07447763532400131</v>
+        <v>0.01581606641411781</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.05428136885166168</v>
+        <v>0.1250293552875519</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.05545477569103241</v>
+        <v>0.02668988518416882</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.09870807826519012</v>
+        <v>0.1107443124055862</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.02244343049824238</v>
+        <v>0.01781728304922581</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1148769706487656</v>
+        <v>0.05443111434578896</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.05116614326834679</v>
+        <v>0.1095997989177704</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002653928473591805</v>
+        <v>0.02370584197342396</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1195070073008537</v>
+        <v>0.1731694489717484</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0493733137845993</v>
+        <v>0.09790202975273132</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.08276353776454926</v>
+        <v>0.002675563097000122</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01443192735314369</v>
+        <v>0.02752858027815819</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.07739616930484772</v>
+        <v>0.08409418165683746</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.03709780424833298</v>
+        <v>0.03572465106844902</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.05083218589425087</v>
+        <v>0.01845326088368893</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0496474951505661</v>
+        <v>0.006952032446861267</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.08972381800413132</v>
+        <v>0.02584262564778328</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1028488725423813</v>
+        <v>0.0955193042755127</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.00104426546022296</v>
+        <v>0.07769735902547836</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.03856758773326874</v>
+        <v>0.08704212307929993</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.007436945103108883</v>
+        <v>0.00494740717113018</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.05782449617981911</v>
+        <v>0.03738659620285034</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.09371455013751984</v>
+        <v>0.02627213299274445</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.09292082488536835</v>
+        <v>0.0694715827703476</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.09507809579372406</v>
+        <v>0.03966242447495461</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.003621325828135014</v>
+        <v>0.004329510033130646</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.1030538976192474</v>
+        <v>0.1620858162641525</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.05312822759151459</v>
+        <v>0.1051332503557205</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.09271460771560669</v>
+        <v>0.001243188977241516</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.004460275638848543</v>
+        <v>0.002370445057749748</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.113041415810585</v>
+        <v>0.1162933856248856</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.02653578110039234</v>
+        <v>0.02668672241270542</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.06788761913776398</v>
+        <v>0.0487859845161438</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.02882041037082672</v>
+        <v>0.002354716416448355</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.04698535054922104</v>
+        <v>0.07670539617538452</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1186125725507736</v>
+        <v>0.2568624019622803</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.04903880134224892</v>
+        <v>0.03859797492623329</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.2131975442171097</v>
+        <v>0.08877018094062805</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1170030981302261</v>
+        <v>0.1858508884906769</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.1357848197221756</v>
+        <v>0.2640727758407593</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.05153507366776466</v>
+        <v>0.0464206263422966</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0899711474776268</v>
+        <v>0.03233620524406433</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.1553600430488586</v>
+        <v>0.01510069705545902</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002584155648946762</v>
+        <v>0.01767498813569546</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0632527619600296</v>
+        <v>0.1394491642713547</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.04028807580471039</v>
+        <v>0.1247415989637375</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03446651622653008</v>
+        <v>0.01917886920273304</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.06074229627847672</v>
+        <v>0.01783963851630688</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.06474532186985016</v>
+        <v>0.03586785495281219</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.07884626090526581</v>
+        <v>0.01745570078492165</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.04249819368124008</v>
+        <v>0.04378635063767433</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.09241620451211929</v>
+        <v>0.02985454723238945</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.03571636229753494</v>
+        <v>0.03918032348155975</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05603781342506409</v>
+        <v>0.008662750013172626</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.08735912293195724</v>
+        <v>0.1577900648117065</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.03222673013806343</v>
+        <v>0.04573134705424309</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.006635523401200771</v>
+        <v>0.1610726416110992</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01774667389690876</v>
+        <v>0.1265652626752853</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.01231231912970543</v>
+        <v>0.1210054755210876</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.007866094820201397</v>
+        <v>0.02257780358195305</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.03534648939967155</v>
+        <v>0.1535227298736572</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.04833899438381195</v>
+        <v>0.01150085590779781</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.1339514255523682</v>
+        <v>0.1276428401470184</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.03901335224509239</v>
+        <v>0.008236031979322433</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.03024380281567574</v>
+        <v>0.0672231912612915</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.07676126807928085</v>
+        <v>0.06571155041456223</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.119772657752037</v>
+        <v>0.05139298364520073</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.04477726668119431</v>
+        <v>0.02237320505082607</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.009476958774030209</v>
+        <v>0.04114484041929245</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.007934616878628731</v>
+        <v>0.002932505216449499</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.01982283778488636</v>
+        <v>0.01381881162524223</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.02994479984045029</v>
+        <v>0.04941472783684731</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.06712863594293594</v>
+        <v>0.01144964154809713</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.06975272297859192</v>
+        <v>0.006782345473766327</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.04535618796944618</v>
+        <v>0.08566786348819733</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01339541655033827</v>
+        <v>0.08521790057420731</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.01145537756383419</v>
+        <v>0.02649510651826859</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.1126989722251892</v>
+        <v>0.00679338164627552</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.02560220286250114</v>
+        <v>0.02781057730317116</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0138028459623456</v>
+        <v>0.02698184736073017</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.09283845871686935</v>
+        <v>0.2011061906814575</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.03472723439335823</v>
+        <v>0.08841311931610107</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.08518427610397339</v>
+        <v>0.002640724182128906</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01174988225102425</v>
+        <v>0.03698131069540977</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.08545350283384323</v>
+        <v>0.09813759475946426</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.04706195741891861</v>
+        <v>0.04220271855592728</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.04635874181985855</v>
+        <v>0.03153925761580467</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0378405898809433</v>
+        <v>0.02029565721750259</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.01425609830766916</v>
+        <v>0.04033080115914345</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.006296522915363312</v>
+        <v>0.1524696350097656</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.04729844257235527</v>
+        <v>0.0707908421754837</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.1135425120592117</v>
+        <v>0.02782496437430382</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0882614403963089</v>
+        <v>0.155209869146347</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.09916162490844727</v>
+        <v>0.08551382273435593</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.03036555089056492</v>
+        <v>0.1137663275003433</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0203782245516777</v>
+        <v>0.095716692507267</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.03229860588908195</v>
+        <v>0.1215048357844353</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.01766800507903099</v>
+        <v>0.1290118396282196</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.2642927765846252</v>
+        <v>0.1933363676071167</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.046649269759655</v>
+        <v>0.1049282550811768</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.1259203404188156</v>
+        <v>0.1224639788269997</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.008938056416809559</v>
+        <v>0.1509375125169754</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03338282555341721</v>
+        <v>0.08248590677976608</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.07300056517124176</v>
+        <v>0.1240008398890495</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.009457651525735855</v>
+        <v>0.1367998421192169</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.005409829318523407</v>
+        <v>0.01087814569473267</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.04312665015459061</v>
+        <v>0.2170366942882538</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.03884280100464821</v>
+        <v>0.05941983312368393</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0225442610681057</v>
+        <v>0.3643571138381958</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.07809961587190628</v>
+        <v>0.0299528818577528</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.1434162557125092</v>
+        <v>0.09225346893072128</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.05082912743091583</v>
+        <v>0.1041928976774216</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.2269318699836731</v>
+        <v>0.01624170504510403</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.07794409990310669</v>
+        <v>0.02617302350699902</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.09792628139257431</v>
+        <v>0.1074485182762146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5.222947947913781e-06</v>
+        <v>0.01358245499432087</v>
       </c>
       <c r="B5" t="n">
-        <v>5.089039768790826e-05</v>
+        <v>0.1503854393959045</v>
       </c>
       <c r="C5" t="n">
-        <v>8.74795932759298e-06</v>
+        <v>0.0327836275100708</v>
       </c>
       <c r="D5" t="n">
-        <v>1.939391950145364e-05</v>
+        <v>0.09516222774982452</v>
       </c>
       <c r="E5" t="n">
-        <v>9.887036867439747e-06</v>
+        <v>0.1403649896383286</v>
       </c>
       <c r="F5" t="n">
-        <v>1.244574377778918e-06</v>
+        <v>0.008886534720659256</v>
       </c>
       <c r="G5" t="n">
-        <v>7.679603868382401e-07</v>
+        <v>0.07323037832975388</v>
       </c>
       <c r="H5" t="n">
-        <v>1.680333753029117e-06</v>
+        <v>0.0009417601395398378</v>
       </c>
       <c r="I5" t="n">
-        <v>1.025443361868383e-05</v>
+        <v>0.0235632099211216</v>
       </c>
       <c r="J5" t="n">
-        <v>2.413356241959264e-06</v>
+        <v>0.01722928322851658</v>
       </c>
       <c r="K5" t="n">
-        <v>4.675919262808748e-05</v>
+        <v>0.1819462031126022</v>
       </c>
       <c r="L5" t="n">
-        <v>4.571004410536261e-06</v>
+        <v>0.06558161228895187</v>
       </c>
       <c r="M5" t="n">
-        <v>1.988132498809136e-05</v>
+        <v>0.1042481288313866</v>
       </c>
       <c r="N5" t="n">
-        <v>8.488907951686997e-06</v>
+        <v>0.1645995825529099</v>
       </c>
       <c r="O5" t="n">
-        <v>1.210193431688822e-06</v>
+        <v>0.00559513783082366</v>
       </c>
       <c r="P5" t="n">
-        <v>3.959194145863876e-07</v>
+        <v>0.03641152754426003</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.980763944535283e-06</v>
+        <v>0.06908178329467773</v>
       </c>
       <c r="R5" t="n">
-        <v>3.243390210627695e-06</v>
+        <v>0.02919930405914783</v>
       </c>
       <c r="S5" t="n">
-        <v>1.767522576301417e-06</v>
+        <v>0.02424090355634689</v>
       </c>
       <c r="T5" t="n">
-        <v>6.899957043060567e-06</v>
+        <v>0.02370070293545723</v>
       </c>
       <c r="U5" t="n">
-        <v>4.179301868134644e-06</v>
+        <v>0.01910877600312233</v>
       </c>
       <c r="V5" t="n">
-        <v>1.973863390958286e-06</v>
+        <v>0.009678826667368412</v>
       </c>
       <c r="W5" t="n">
-        <v>7.149849807319697e-06</v>
+        <v>0.006062706932425499</v>
       </c>
       <c r="X5" t="n">
-        <v>7.040777290967526e-06</v>
+        <v>0.03390470892190933</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.98399163511931e-06</v>
+        <v>0.003044552868232131</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.980591429808555e-07</v>
+        <v>0.00715089775621891</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.480572331682197e-06</v>
+        <v>0.01252731028944254</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.761252840689849e-06</v>
+        <v>0.03392300009727478</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.205949153401889e-07</v>
+        <v>0.06149961426854134</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.316128646067227e-06</v>
+        <v>0.01586808264255524</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.568855506979162e-06</v>
+        <v>0.007282465696334839</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.777003601295291e-06</v>
+        <v>0.04763785377144814</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.508866148469679e-06</v>
+        <v>0.01925474219024181</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.794894615159137e-06</v>
+        <v>0.02701034769415855</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.815677251215675e-06</v>
+        <v>0.01388232689350843</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.324197339476086e-06</v>
+        <v>0.02092335000634193</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.578617116138048e-06</v>
+        <v>0.02204715646803379</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.002505309268599e-06</v>
+        <v>0.007415092550218105</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.159041798677208e-07</v>
+        <v>0.03471748903393745</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.56573513172043e-07</v>
+        <v>0.02589615434408188</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.947213255945826e-06</v>
+        <v>0.01289101503789425</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.82109157423838e-06</v>
+        <v>0.01105419732630253</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.598775154183386e-06</v>
+        <v>0.02913858741521835</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.760748768399935e-06</v>
+        <v>0.0138601828366518</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.617945705831517e-07</v>
+        <v>0.004863583017140627</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.415318123094039e-06</v>
+        <v>0.007849421352148056</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.778172893158626e-05</v>
+        <v>0.07605147361755371</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.094698513450567e-06</v>
+        <v>0.03894449770450592</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.72346413921332e-06</v>
+        <v>0.02458574064075947</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.211263325894834e-07</v>
+        <v>0.0970001220703125</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.071936463238671e-06</v>
+        <v>0.01038222014904022</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.258880729437806e-06</v>
+        <v>0.01539716962724924</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.839540906687034e-06</v>
+        <v>4.98745939694345e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.174488135002321e-06</v>
+        <v>0.02414682693779469</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.501753442629706e-06</v>
+        <v>0.05273425951600075</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.762159809004515e-05</v>
+        <v>0.01392779126763344</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.415871611243347e-05</v>
+        <v>0.001816167496144772</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.373238880361896e-06</v>
+        <v>0.005147704388946295</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.922395863919519e-06</v>
+        <v>0.05137845128774643</v>
       </c>
       <c r="BH5" t="n">
-        <v>1.686640302978049e-06</v>
+        <v>0.0342872329056263</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.065966216629022e-06</v>
+        <v>0.03673966974020004</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6.081481842556968e-06</v>
+        <v>0.0157571155577898</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.730886419361923e-06</v>
+        <v>0.004197643604129553</v>
       </c>
       <c r="BL5" t="n">
-        <v>7.589265351271024e-06</v>
+        <v>0.03113438934087753</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.082391918316716e-06</v>
+        <v>0.01196254510432482</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.806657903420273e-06</v>
+        <v>0.0004414506256580353</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.474877641769126e-07</v>
+        <v>0.04609115794301033</v>
       </c>
       <c r="BP5" t="n">
-        <v>9.889795364870224e-06</v>
+        <v>0.05488688126206398</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.128059223759919e-06</v>
+        <v>0.02217121794819832</v>
       </c>
       <c r="BR5" t="n">
-        <v>1.757618292685947e-06</v>
+        <v>0.009473271667957306</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.102016530145193e-06</v>
+        <v>0.01248263381421566</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.712995516660158e-07</v>
+        <v>0.01549732312560081</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.799658088610158e-06</v>
+        <v>0.002238696906715631</v>
       </c>
       <c r="BV5" t="n">
-        <v>1.376964155497262e-05</v>
+        <v>0.03481278941035271</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.91909850097727e-06</v>
+        <v>0.01897440291941166</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.673187165986747e-06</v>
+        <v>0.01635820046067238</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.129527825280093e-06</v>
+        <v>0.02796719782054424</v>
       </c>
       <c r="BZ5" t="n">
-        <v>6.476253929577069e-06</v>
+        <v>0.02556691132485867</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.156528014689684e-06</v>
+        <v>0.006654077209532261</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.463849679974373e-06</v>
+        <v>0.002638670383021235</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.391738919664931e-06</v>
+        <v>0.0160038024187088</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.010599021356029e-06</v>
+        <v>0.003792195115238428</v>
       </c>
       <c r="CE5" t="n">
-        <v>7.908483894425444e-06</v>
+        <v>0.03985878452658653</v>
       </c>
       <c r="CF5" t="n">
-        <v>1.493473860136874e-06</v>
+        <v>0.002585344016551971</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.002809651457937e-06</v>
+        <v>0.03166253119707108</v>
       </c>
       <c r="CH5" t="n">
-        <v>2.620386339913239e-06</v>
+        <v>0.02631770819425583</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.204523840669935e-07</v>
+        <v>0.007228317204862833</v>
       </c>
       <c r="CJ5" t="n">
-        <v>9.719099125504727e-07</v>
+        <v>0.009620477445423603</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.09709617390763e-07</v>
+        <v>0.004417345393449068</v>
       </c>
       <c r="CL5" t="n">
-        <v>8.66797279286402e-07</v>
+        <v>0.009291707538068295</v>
       </c>
       <c r="CM5" t="n">
-        <v>9.136547305388376e-06</v>
+        <v>0.09097439795732498</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.072941571095726e-06</v>
+        <v>0.03464154899120331</v>
       </c>
       <c r="CO5" t="n">
-        <v>2.458505832692026e-06</v>
+        <v>0.01265050377696753</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.618297119421186e-06</v>
+        <v>0.005355351604521275</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.213640280184336e-05</v>
+        <v>0.00412857485935092</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.022982451104326e-05</v>
+        <v>0.004566271789371967</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.381106130793341e-06</v>
+        <v>0.01481626182794571</v>
       </c>
       <c r="CT5" t="n">
-        <v>6.406250122381607e-06</v>
+        <v>0.03306679800152779</v>
       </c>
       <c r="CU5" t="n">
-        <v>6.684695563308196e-06</v>
+        <v>0.01394122559577227</v>
       </c>
       <c r="CV5" t="n">
-        <v>8.245893354796863e-07</v>
+        <v>0.004545767325907946</v>
       </c>
       <c r="CW5" t="n">
-        <v>7.234421445900807e-06</v>
+        <v>0.03364476189017296</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.819152089410636e-06</v>
+        <v>0.01191054750233889</v>
       </c>
       <c r="CY5" t="n">
-        <v>3.265422037657117e-06</v>
+        <v>0.02619881927967072</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.422978584741941e-06</v>
+        <v>0.02473129518330097</v>
       </c>
       <c r="DA5" t="n">
-        <v>5.183762823435245e-07</v>
+        <v>0.00835136603564024</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.04929290500877e-06</v>
+        <v>0.01058181282132864</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.335294427917688e-06</v>
+        <v>0.006450135260820389</v>
       </c>
       <c r="DD5" t="n">
-        <v>8.598125305070425e-07</v>
+        <v>0.01021494064480066</v>
       </c>
       <c r="DE5" t="n">
-        <v>4.004963102488546e-06</v>
+        <v>0.006132462061941624</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.279896332562203e-05</v>
+        <v>0.01759746670722961</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.647331595857395e-06</v>
+        <v>0.04011176526546478</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.545510167488828e-05</v>
+        <v>0.004446721635758877</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.006628372124396e-05</v>
+        <v>0.1122124716639519</v>
       </c>
       <c r="DJ5" t="n">
-        <v>6.986528205743525e-06</v>
+        <v>0.0015607716049999</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.589039240774582e-07</v>
+        <v>0.0318433977663517</v>
       </c>
       <c r="DL5" t="n">
-        <v>5.025543714509695e-07</v>
+        <v>0.0008908340241760015</v>
       </c>
       <c r="DM5" t="n">
-        <v>3.820672191068297e-06</v>
+        <v>0.04274255782365799</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.063056288330699e-06</v>
+        <v>0.0126333013176918</v>
       </c>
       <c r="DO5" t="n">
-        <v>6.549092177010607e-06</v>
+        <v>0.009272418916225433</v>
       </c>
       <c r="DP5" t="n">
-        <v>3.57105272996705e-06</v>
+        <v>0.004285665694624186</v>
       </c>
       <c r="DQ5" t="n">
-        <v>4.749903382617049e-06</v>
+        <v>0.0191476009786129</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.20696766115725e-06</v>
+        <v>0.001883032498881221</v>
       </c>
       <c r="DS5" t="n">
-        <v>6.044069777999539e-06</v>
+        <v>0.02850121818482876</v>
       </c>
       <c r="DT5" t="n">
-        <v>3.89952037949115e-06</v>
+        <v>0.002410013228654861</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.617404109310883e-06</v>
+        <v>0.007808214519172907</v>
       </c>
       <c r="DV5" t="n">
-        <v>5.829782168120801e-08</v>
+        <v>0.0110637079924345</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.301461111324898e-06</v>
+        <v>0.03481599688529968</v>
       </c>
       <c r="DX5" t="n">
-        <v>7.784820809320081e-06</v>
+        <v>0.02228008583188057</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.648560777946841e-07</v>
+        <v>0.01445438247174025</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.473183930211235e-06</v>
+        <v>0.008682196028530598</v>
       </c>
       <c r="EA5" t="n">
-        <v>3.863341589749325e-06</v>
+        <v>0.005806019064038992</v>
       </c>
       <c r="EB5" t="n">
-        <v>5.855516064912081e-06</v>
+        <v>0.02810773439705372</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.160691908808076e-06</v>
+        <v>0.02590077556669712</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.422792820449104e-06</v>
+        <v>0.007227766793221235</v>
       </c>
       <c r="EE5" t="n">
-        <v>3.1918632430461e-06</v>
+        <v>0.02189558930695057</v>
       </c>
       <c r="EF5" t="n">
-        <v>2.438954652461689e-06</v>
+        <v>0.005732093937695026</v>
       </c>
       <c r="EG5" t="n">
-        <v>8.563872142985929e-06</v>
+        <v>0.05979698896408081</v>
       </c>
       <c r="EH5" t="n">
-        <v>1.112726295104949e-06</v>
+        <v>0.01696735247969627</v>
       </c>
       <c r="EI5" t="n">
-        <v>3.333434051455697e-06</v>
+        <v>0.0273605827242136</v>
       </c>
       <c r="EJ5" t="n">
-        <v>4.994023129256675e-06</v>
+        <v>0.0437200702726841</v>
       </c>
       <c r="EK5" t="n">
-        <v>6.092762305343058e-06</v>
+        <v>0.02781687118113041</v>
       </c>
       <c r="EL5" t="n">
-        <v>9.120710160459566e-07</v>
+        <v>0.007096584886312485</v>
       </c>
       <c r="EM5" t="n">
-        <v>2.030786617979174e-06</v>
+        <v>0.00871177576482296</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.326854317085235e-06</v>
+        <v>0.005006898194551468</v>
       </c>
       <c r="EO5" t="n">
-        <v>3.725821670741425e-06</v>
+        <v>0.001383662223815918</v>
       </c>
       <c r="EP5" t="n">
-        <v>2.797472461679718e-06</v>
+        <v>0.01446598395705223</v>
       </c>
       <c r="EQ5" t="n">
-        <v>7.604010079376167e-06</v>
+        <v>0.00883288960903883</v>
       </c>
       <c r="ER5" t="n">
-        <v>2.324329443581519e-06</v>
+        <v>0.02239870838820934</v>
       </c>
       <c r="ES5" t="n">
-        <v>4.016048933408456e-06</v>
+        <v>0.02147217281162739</v>
       </c>
       <c r="ET5" t="n">
-        <v>6.366059892570775e-07</v>
+        <v>0.002885548863559961</v>
       </c>
       <c r="EU5" t="n">
-        <v>1.004955379357853e-06</v>
+        <v>0.01387387234717607</v>
       </c>
       <c r="EV5" t="n">
-        <v>1.429891653970117e-06</v>
+        <v>0.01052499189972878</v>
       </c>
       <c r="EW5" t="n">
-        <v>4.117973162465205e-07</v>
+        <v>0.0245398972183466</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.343869709875435e-06</v>
+        <v>0.006150299683213234</v>
       </c>
       <c r="EY5" t="n">
-        <v>7.57077532398398e-06</v>
+        <v>0.04293276369571686</v>
       </c>
       <c r="EZ5" t="n">
-        <v>7.343144261540147e-07</v>
+        <v>0.007731092162430286</v>
       </c>
       <c r="FA5" t="n">
-        <v>3.390510073586483e-06</v>
+        <v>0.02866404503583908</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.514221594334231e-06</v>
+        <v>0.01804390549659729</v>
       </c>
       <c r="FC5" t="n">
-        <v>1.925140850289608e-06</v>
+        <v>0.004361853469163179</v>
       </c>
       <c r="FD5" t="n">
-        <v>4.302070522044232e-07</v>
+        <v>0.01599119044840336</v>
       </c>
       <c r="FE5" t="n">
-        <v>7.79240735937492e-07</v>
+        <v>0.001515134703367949</v>
       </c>
       <c r="FF5" t="n">
-        <v>8.870408123584639e-07</v>
+        <v>0.004817819222807884</v>
       </c>
       <c r="FG5" t="n">
-        <v>1.045168431801358e-07</v>
+        <v>0.01104388572275639</v>
       </c>
       <c r="FH5" t="n">
-        <v>2.048782334895805e-06</v>
+        <v>0.00863645039498806</v>
       </c>
       <c r="FI5" t="n">
-        <v>2.110005539179838e-07</v>
+        <v>0.02093991078436375</v>
       </c>
       <c r="FJ5" t="n">
-        <v>1.588540840202768e-06</v>
+        <v>0.01751230470836163</v>
       </c>
       <c r="FK5" t="n">
-        <v>4.859359250986017e-06</v>
+        <v>0.04665795713663101</v>
       </c>
       <c r="FL5" t="n">
-        <v>9.038642929226626e-06</v>
+        <v>0.01938008703291416</v>
       </c>
       <c r="FM5" t="n">
-        <v>1.20492381938675e-06</v>
+        <v>0.004477753769606352</v>
       </c>
       <c r="FN5" t="n">
-        <v>3.574071456569072e-07</v>
+        <v>0.005426126532256603</v>
       </c>
       <c r="FO5" t="n">
-        <v>2.132392637577141e-06</v>
+        <v>0.03445316106081009</v>
       </c>
       <c r="FP5" t="n">
-        <v>4.602930403052596e-06</v>
+        <v>0.01405245997011662</v>
       </c>
       <c r="FQ5" t="n">
-        <v>3.062461701119901e-06</v>
+        <v>0.06535252928733826</v>
       </c>
       <c r="FR5" t="n">
-        <v>6.445359304052545e-06</v>
+        <v>0.02637098729610443</v>
       </c>
       <c r="FS5" t="n">
-        <v>1.386306030326523e-05</v>
+        <v>0.01489879656583071</v>
       </c>
       <c r="FT5" t="n">
-        <v>3.02122452922049e-06</v>
+        <v>0.09007330238819122</v>
       </c>
       <c r="FU5" t="n">
-        <v>4.75811702926876e-07</v>
+        <v>0.01531887054443359</v>
       </c>
       <c r="FV5" t="n">
-        <v>1.143321014751564e-06</v>
+        <v>0.02549031563103199</v>
       </c>
       <c r="FW5" t="n">
-        <v>5.02890907227993e-06</v>
+        <v>0.01492040231823921</v>
       </c>
       <c r="FX5" t="n">
-        <v>4.994786650058813e-06</v>
+        <v>0.005492320284247398</v>
       </c>
       <c r="FY5" t="n">
-        <v>6.230824055819539e-06</v>
+        <v>0.01225772686302662</v>
       </c>
       <c r="FZ5" t="n">
-        <v>5.64049855711346e-07</v>
+        <v>0.03883391991257668</v>
       </c>
       <c r="GA5" t="n">
-        <v>3.575214350348688e-06</v>
+        <v>0.03621754050254822</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.446053374820622e-06</v>
+        <v>0.03485573083162308</v>
       </c>
       <c r="GC5" t="n">
-        <v>4.606185484590242e-06</v>
+        <v>0.05634435638785362</v>
       </c>
       <c r="GD5" t="n">
-        <v>4.08171399612911e-06</v>
+        <v>0.02420512400567532</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.410656861684402e-06</v>
+        <v>0.03844985365867615</v>
       </c>
       <c r="GF5" t="n">
-        <v>4.987221018382115e-06</v>
+        <v>0.02186678908765316</v>
       </c>
       <c r="GG5" t="n">
-        <v>4.590103799273493e-06</v>
+        <v>0.01538452971726656</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4.791655101143988e-06</v>
+        <v>0.001910414313897491</v>
       </c>
       <c r="B6" t="n">
-        <v>4.448219260666519e-05</v>
+        <v>0.03083635307848454</v>
       </c>
       <c r="C6" t="n">
-        <v>4.372904186311644e-06</v>
+        <v>0.02417850680649281</v>
       </c>
       <c r="D6" t="n">
-        <v>1.595905814610887e-05</v>
+        <v>0.02182943560183048</v>
       </c>
       <c r="E6" t="n">
-        <v>1.862173348854412e-07</v>
+        <v>0.01658472418785095</v>
       </c>
       <c r="F6" t="n">
-        <v>3.437605846556835e-05</v>
+        <v>0.06510470062494278</v>
       </c>
       <c r="G6" t="n">
-        <v>9.674828334027552e-07</v>
+        <v>0.01468697004020214</v>
       </c>
       <c r="H6" t="n">
-        <v>1.050873015628895e-05</v>
+        <v>0.01627519726753235</v>
       </c>
       <c r="I6" t="n">
-        <v>6.065587854209298e-07</v>
+        <v>0.002790940459817648</v>
       </c>
       <c r="J6" t="n">
-        <v>1.440777759853518e-05</v>
+        <v>0.01699613779783249</v>
       </c>
       <c r="K6" t="n">
-        <v>3.367928002262488e-05</v>
+        <v>0.03702874854207039</v>
       </c>
       <c r="L6" t="n">
-        <v>3.59812838723883e-06</v>
+        <v>0.04263462126255035</v>
       </c>
       <c r="M6" t="n">
-        <v>1.474762211728375e-05</v>
+        <v>0.02173752337694168</v>
       </c>
       <c r="N6" t="n">
-        <v>1.837522518144397e-06</v>
+        <v>0.02159727364778519</v>
       </c>
       <c r="O6" t="n">
-        <v>2.833339567587245e-05</v>
+        <v>0.07782060652971268</v>
       </c>
       <c r="P6" t="n">
-        <v>2.275297902087914e-06</v>
+        <v>0.001926436088979244</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.165280188317411e-06</v>
+        <v>0.01987604238092899</v>
       </c>
       <c r="R6" t="n">
-        <v>4.322702125136857e-07</v>
+        <v>0.001737334998324513</v>
       </c>
       <c r="S6" t="n">
-        <v>3.943566298403312e-06</v>
+        <v>0.001499940059147775</v>
       </c>
       <c r="T6" t="n">
-        <v>1.068507458512613e-06</v>
+        <v>0.01673873327672482</v>
       </c>
       <c r="U6" t="n">
-        <v>2.216223947471008e-06</v>
+        <v>0.006551729515194893</v>
       </c>
       <c r="V6" t="n">
-        <v>3.501143964967923e-06</v>
+        <v>0.004146777093410492</v>
       </c>
       <c r="W6" t="n">
-        <v>3.061258894376806e-06</v>
+        <v>0.01489345170557499</v>
       </c>
       <c r="X6" t="n">
-        <v>2.777773715934018e-06</v>
+        <v>0.005589680746197701</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.584031901482376e-06</v>
+        <v>0.009473861195147038</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.105049477700959e-06</v>
+        <v>0.005901042371988297</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.359353170002578e-06</v>
+        <v>0.005651457700878382</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.852177433647739e-06</v>
+        <v>0.001447138842195272</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.845037776452955e-06</v>
+        <v>0.01819910109043121</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.758884699640475e-07</v>
+        <v>0.008389687165617943</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.975618255935842e-06</v>
+        <v>0.001674233353696764</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.143890681822086e-07</v>
+        <v>0.02040409296751022</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.448280784188682e-07</v>
+        <v>0.01725663430988789</v>
       </c>
       <c r="AH6" t="n">
-        <v>9.864023695627111e-07</v>
+        <v>0.004362084902822971</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.386809789342806e-07</v>
+        <v>0.01694796793162823</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.277495925933181e-06</v>
+        <v>0.007308703381568193</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.349788021798304e-06</v>
+        <v>0.00734275858849287</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.690329205914168e-06</v>
+        <v>0.008033955469727516</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.001296141112107e-06</v>
+        <v>0.00652479100972414</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.821617949346546e-07</v>
+        <v>0.01251166686415672</v>
       </c>
       <c r="AO6" t="n">
-        <v>4.329164312366629e-06</v>
+        <v>0.01712680421769619</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.364948371308856e-06</v>
+        <v>0.000122754427138716</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.336046011601866e-07</v>
+        <v>0.007229851093143225</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2187573967567e-07</v>
+        <v>0.01287626475095749</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.063360393047333e-06</v>
+        <v>0.002766028046607971</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.690907876967685e-06</v>
+        <v>0.005111473612487316</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.631788290978875e-05</v>
+        <v>0.0242822952568531</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.380754156343755e-06</v>
+        <v>0.02251503989100456</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.13743202140904e-06</v>
+        <v>0.01122364401817322</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.554571210566792e-06</v>
+        <v>0.01464004162698984</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.179902003263123e-05</v>
+        <v>0.06238792091608047</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.912698391810409e-06</v>
+        <v>0.009169070050120354</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.034858136492403e-07</v>
+        <v>0.02146720699965954</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.857469427108299e-06</v>
+        <v>0.005032620392739773</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.996581083105411e-06</v>
+        <v>0.02004477754235268</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.877053000498563e-05</v>
+        <v>0.03363555297255516</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.733873877034057e-06</v>
+        <v>0.01445204019546509</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.137532065826235e-06</v>
+        <v>0.01339852064847946</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.226903911330737e-06</v>
+        <v>0.003996121697127819</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.625928457040573e-06</v>
+        <v>0.004701745696365833</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.7928556417246e-07</v>
+        <v>0.00936136394739151</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.178773686660861e-06</v>
+        <v>0.005573730450123549</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.563285422889749e-06</v>
+        <v>0.006245008669793606</v>
       </c>
       <c r="BL6" t="n">
-        <v>8.251156486949185e-07</v>
+        <v>0.007931789383292198</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.417121873411816e-06</v>
+        <v>0.00515228183940053</v>
       </c>
       <c r="BN6" t="n">
-        <v>8.606289156887215e-07</v>
+        <v>0.008673654869198799</v>
       </c>
       <c r="BO6" t="n">
-        <v>8.366772021872748e-07</v>
+        <v>0.0001616152003407478</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.84650298251654e-06</v>
+        <v>0.005686272867023945</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.497396851846133e-06</v>
+        <v>0.00302418228238821</v>
       </c>
       <c r="BR6" t="n">
-        <v>1.402906718794839e-06</v>
+        <v>0.006461658515036106</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.244033334543929e-06</v>
+        <v>0.005346918012946844</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.79974108505121e-07</v>
+        <v>0.01095423009246588</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.639615675230743e-06</v>
+        <v>0.005007966887205839</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.449021490581799e-06</v>
+        <v>0.02825744822621346</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.952418748871423e-06</v>
+        <v>0.01250167842954397</v>
       </c>
       <c r="BX6" t="n">
-        <v>4.495600933296373e-06</v>
+        <v>0.01321005262434483</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.097686087334296e-06</v>
+        <v>0.01748309098184109</v>
       </c>
       <c r="BZ6" t="n">
-        <v>7.82183269620873e-06</v>
+        <v>0.03083185292780399</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.305567022631294e-06</v>
+        <v>0.00151822401676327</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.517031478215358e-07</v>
+        <v>0.007644754834473133</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.647919467970496e-06</v>
+        <v>0.003445801325142384</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.597619530002703e-06</v>
+        <v>0.004061592277139425</v>
       </c>
       <c r="CE6" t="n">
-        <v>6.783020580769517e-06</v>
+        <v>0.01301407814025879</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.658836820046417e-06</v>
+        <v>0.002290276810526848</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.378992803642177e-06</v>
+        <v>0.003967635333538055</v>
       </c>
       <c r="CH6" t="n">
-        <v>5.495734853866452e-07</v>
+        <v>0.004858705680817366</v>
       </c>
       <c r="CI6" t="n">
-        <v>5.599459200311685e-06</v>
+        <v>0.01306429877877235</v>
       </c>
       <c r="CJ6" t="n">
-        <v>9.100025408770307e-07</v>
+        <v>0.0008293581195175648</v>
       </c>
       <c r="CK6" t="n">
-        <v>2.304106146766571e-06</v>
+        <v>5.483254790306091e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>3.265786745032528e-06</v>
+        <v>0.005926165729761124</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.468858499720227e-06</v>
+        <v>0.01547880563884974</v>
       </c>
       <c r="CN6" t="n">
-        <v>4.618089519681234e-07</v>
+        <v>0.006875196006149054</v>
       </c>
       <c r="CO6" t="n">
-        <v>5.315257567417575e-07</v>
+        <v>0.01943748071789742</v>
       </c>
       <c r="CP6" t="n">
-        <v>3.505747372400947e-06</v>
+        <v>0.02381113357841969</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.117794105695793e-06</v>
+        <v>0.001190671930089593</v>
       </c>
       <c r="CR6" t="n">
-        <v>3.07019445244805e-06</v>
+        <v>0.001828613225370646</v>
       </c>
       <c r="CS6" t="n">
-        <v>4.400371835799888e-06</v>
+        <v>0.005908563733100891</v>
       </c>
       <c r="CT6" t="n">
-        <v>4.993475613446208e-06</v>
+        <v>0.001218601479195058</v>
       </c>
       <c r="CU6" t="n">
-        <v>9.647477554608486e-07</v>
+        <v>0.008346816524863243</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.112888071475027e-06</v>
+        <v>0.0074491361156106</v>
       </c>
       <c r="CW6" t="n">
-        <v>5.933034117333591e-06</v>
+        <v>0.01415546517819166</v>
       </c>
       <c r="CX6" t="n">
-        <v>2.742577180470107e-06</v>
+        <v>0.004535896237939596</v>
       </c>
       <c r="CY6" t="n">
-        <v>3.705585413626977e-06</v>
+        <v>0.002122401725500822</v>
       </c>
       <c r="CZ6" t="n">
-        <v>7.417556844302453e-07</v>
+        <v>0.001916914945468307</v>
       </c>
       <c r="DA6" t="n">
-        <v>6.779286195524037e-06</v>
+        <v>0.01680195517838001</v>
       </c>
       <c r="DB6" t="n">
-        <v>5.05727712152293e-07</v>
+        <v>0.001392720732837915</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.252974920542329e-06</v>
+        <v>0.0005227219080552459</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.378720298816916e-06</v>
+        <v>0.003205538727343082</v>
       </c>
       <c r="DE6" t="n">
-        <v>8.605728112343058e-07</v>
+        <v>0.0004187986487522721</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.447423619538313e-05</v>
+        <v>0.008846264332532883</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.404088374736602e-06</v>
+        <v>0.02912196516990662</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.535624141979497e-05</v>
+        <v>0.0008620410226285458</v>
       </c>
       <c r="DI6" t="n">
-        <v>5.536008984563523e-07</v>
+        <v>0.0157165452837944</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.778789282980142e-06</v>
+        <v>0.02627248503267765</v>
       </c>
       <c r="DK6" t="n">
-        <v>2.605906047392637e-06</v>
+        <v>0.001106953946873546</v>
       </c>
       <c r="DL6" t="n">
-        <v>1.16780129246763e-05</v>
+        <v>0.004585583694279194</v>
       </c>
       <c r="DM6" t="n">
-        <v>3.579448730306467e-06</v>
+        <v>0.005941544659435749</v>
       </c>
       <c r="DN6" t="n">
-        <v>7.798452088536578e-07</v>
+        <v>0.004048188216984272</v>
       </c>
       <c r="DO6" t="n">
-        <v>5.761452484875917e-06</v>
+        <v>0.02268485352396965</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.021919047161646e-06</v>
+        <v>0.002875940408557653</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.719572395586511e-07</v>
+        <v>0.005210448056459427</v>
       </c>
       <c r="DR6" t="n">
-        <v>1.335503156951745e-06</v>
+        <v>0.0004295310936868191</v>
       </c>
       <c r="DS6" t="n">
-        <v>3.824349619208078e-07</v>
+        <v>0.01134170405566692</v>
       </c>
       <c r="DT6" t="n">
-        <v>2.401566689513857e-06</v>
+        <v>0.0002451456093695015</v>
       </c>
       <c r="DU6" t="n">
-        <v>1.779816329872119e-07</v>
+        <v>0.01097276713699102</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.551471309037879e-06</v>
+        <v>0.008695623837411404</v>
       </c>
       <c r="DW6" t="n">
-        <v>1.654855395827326e-06</v>
+        <v>0.005526274908334017</v>
       </c>
       <c r="DX6" t="n">
-        <v>3.587195124055143e-06</v>
+        <v>0.00467062508687377</v>
       </c>
       <c r="DY6" t="n">
-        <v>4.796278290086775e-07</v>
+        <v>0.009224001318216324</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.690331941972545e-06</v>
+        <v>0.01403720304369926</v>
       </c>
       <c r="EA6" t="n">
-        <v>2.069962647510692e-06</v>
+        <v>0.002088228240609169</v>
       </c>
       <c r="EB6" t="n">
-        <v>5.995076662657084e-06</v>
+        <v>0.01695873960852623</v>
       </c>
       <c r="EC6" t="n">
-        <v>7.033336260064971e-07</v>
+        <v>0.0009981726761907339</v>
       </c>
       <c r="ED6" t="n">
-        <v>1.392759941154509e-06</v>
+        <v>0.002858156338334084</v>
       </c>
       <c r="EE6" t="n">
-        <v>2.258318545500515e-06</v>
+        <v>0.005659967195242643</v>
       </c>
       <c r="EF6" t="n">
-        <v>3.431855475355405e-07</v>
+        <v>0.003963658586144447</v>
       </c>
       <c r="EG6" t="n">
-        <v>1.637866489545559e-06</v>
+        <v>0.009098943322896957</v>
       </c>
       <c r="EH6" t="n">
-        <v>3.119630264336593e-06</v>
+        <v>0.005751282908022404</v>
       </c>
       <c r="EI6" t="n">
-        <v>8.588227728978381e-07</v>
+        <v>0.004642811603844166</v>
       </c>
       <c r="EJ6" t="n">
-        <v>2.373101608554862e-07</v>
+        <v>0.001825789455324411</v>
       </c>
       <c r="EK6" t="n">
-        <v>5.347083515516715e-06</v>
+        <v>0.00245282263495028</v>
       </c>
       <c r="EL6" t="n">
-        <v>6.18231865701091e-07</v>
+        <v>0.004975578282028437</v>
       </c>
       <c r="EM6" t="n">
-        <v>4.321164226439578e-08</v>
+        <v>0.00066933105699718</v>
       </c>
       <c r="EN6" t="n">
-        <v>1.621638261894986e-06</v>
+        <v>0.0006973502459004521</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.542917743790895e-06</v>
+        <v>0.008018506690859795</v>
       </c>
       <c r="EP6" t="n">
-        <v>2.876739927160088e-06</v>
+        <v>0.00104636768810451</v>
       </c>
       <c r="EQ6" t="n">
-        <v>1.519871375421644e-06</v>
+        <v>0.004624282941222191</v>
       </c>
       <c r="ER6" t="n">
-        <v>7.618557447131025e-07</v>
+        <v>0.0003074952983297408</v>
       </c>
       <c r="ES6" t="n">
-        <v>1.006128286462626e-06</v>
+        <v>0.007440324407070875</v>
       </c>
       <c r="ET6" t="n">
-        <v>3.102741175098345e-08</v>
+        <v>0.001725764712318778</v>
       </c>
       <c r="EU6" t="n">
-        <v>1.803096552066563e-07</v>
+        <v>0.0003588493273127824</v>
       </c>
       <c r="EV6" t="n">
-        <v>8.173441528924741e-06</v>
+        <v>0.000356561504304409</v>
       </c>
       <c r="EW6" t="n">
-        <v>1.052588231686968e-06</v>
+        <v>0.007232426665723324</v>
       </c>
       <c r="EX6" t="n">
-        <v>1.194043306895765e-06</v>
+        <v>0.00308806705288589</v>
       </c>
       <c r="EY6" t="n">
-        <v>5.639355549647007e-06</v>
+        <v>0.01562569476664066</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1.243054953192768e-06</v>
+        <v>0.001689870376139879</v>
       </c>
       <c r="FA6" t="n">
-        <v>2.683934326341841e-06</v>
+        <v>0.00197482923977077</v>
       </c>
       <c r="FB6" t="n">
-        <v>2.572488426721975e-07</v>
+        <v>0.0012828737962991</v>
       </c>
       <c r="FC6" t="n">
-        <v>6.111216407589382e-06</v>
+        <v>0.01433791778981686</v>
       </c>
       <c r="FD6" t="n">
-        <v>1.79568235125771e-06</v>
+        <v>0.001993029844015837</v>
       </c>
       <c r="FE6" t="n">
-        <v>2.858344714695704e-06</v>
+        <v>0.0002833189209923148</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.520119323889958e-06</v>
+        <v>0.0001631692284718156</v>
       </c>
       <c r="FG6" t="n">
-        <v>2.799479261739179e-06</v>
+        <v>0.0006579230539500713</v>
       </c>
       <c r="FH6" t="n">
-        <v>2.85306623482029e-06</v>
+        <v>0.01376233994960785</v>
       </c>
       <c r="FI6" t="n">
-        <v>8.340651902472018e-07</v>
+        <v>0.01586947403848171</v>
       </c>
       <c r="FJ6" t="n">
-        <v>7.052725777612068e-06</v>
+        <v>0.004249533638358116</v>
       </c>
       <c r="FK6" t="n">
-        <v>5.074705882179842e-07</v>
+        <v>0.006187496706843376</v>
       </c>
       <c r="FL6" t="n">
-        <v>6.123487764853053e-06</v>
+        <v>0.009665193967521191</v>
       </c>
       <c r="FM6" t="n">
-        <v>6.737002991030749e-07</v>
+        <v>0.005398839712142944</v>
       </c>
       <c r="FN6" t="n">
-        <v>9.851924005488399e-07</v>
+        <v>0.01946227997541428</v>
       </c>
       <c r="FO6" t="n">
-        <v>1.578543788127718e-06</v>
+        <v>0.02532191015779972</v>
       </c>
       <c r="FP6" t="n">
-        <v>4.148035259277094e-06</v>
+        <v>0.0026159449480474</v>
       </c>
       <c r="FQ6" t="n">
-        <v>1.867408172984142e-06</v>
+        <v>0.02099593169987202</v>
       </c>
       <c r="FR6" t="n">
-        <v>3.148330279145739e-06</v>
+        <v>0.01185846514999866</v>
       </c>
       <c r="FS6" t="n">
-        <v>6.360536985994258e-07</v>
+        <v>0.01954101398587227</v>
       </c>
       <c r="FT6" t="n">
-        <v>1.093193714041263e-05</v>
+        <v>0.003119183704257011</v>
       </c>
       <c r="FU6" t="n">
-        <v>3.227386287107947e-06</v>
+        <v>0.02501836232841015</v>
       </c>
       <c r="FV6" t="n">
-        <v>2.191857674915809e-06</v>
+        <v>0.02436410263180733</v>
       </c>
       <c r="FW6" t="n">
-        <v>2.590709868854901e-07</v>
+        <v>0.01810500584542751</v>
       </c>
       <c r="FX6" t="n">
-        <v>3.644560820248444e-06</v>
+        <v>0.005629573483020067</v>
       </c>
       <c r="FY6" t="n">
-        <v>4.536452706815908e-06</v>
+        <v>0.006194140762090683</v>
       </c>
       <c r="FZ6" t="n">
-        <v>2.269809726840322e-07</v>
+        <v>0.005286768544465303</v>
       </c>
       <c r="GA6" t="n">
-        <v>2.446086455165641e-06</v>
+        <v>0.01518811751157045</v>
       </c>
       <c r="GB6" t="n">
-        <v>8.324627742695156e-07</v>
+        <v>0.003541415790095925</v>
       </c>
       <c r="GC6" t="n">
-        <v>1.395868184772553e-05</v>
+        <v>0.003431608667597175</v>
       </c>
       <c r="GD6" t="n">
-        <v>5.701191639673198e-06</v>
+        <v>0.01619333028793335</v>
       </c>
       <c r="GE6" t="n">
-        <v>9.244489774573594e-06</v>
+        <v>0.005797923542559147</v>
       </c>
       <c r="GF6" t="n">
-        <v>8.307205234814319e-08</v>
+        <v>0.004745330195873976</v>
       </c>
       <c r="GG6" t="n">
-        <v>9.338262429992028e-07</v>
+        <v>0.007085929159075022</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0004435358860064298</v>
+        <v>0.2002732455730438</v>
       </c>
       <c r="B7" t="n">
-        <v>0.005284911021590233</v>
+        <v>0.5948129892349243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0005149442586116493</v>
+        <v>0.09501439332962036</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003160373773425817</v>
+        <v>0.06772416830062866</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003761820844374597</v>
+        <v>0.02314966171979904</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003502652049064636</v>
+        <v>0.6322529315948486</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002574520767666399</v>
+        <v>0.08414322137832642</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00129289086908102</v>
+        <v>0.2886824309825897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001018021212075837</v>
+        <v>0.01259816065430641</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001128350151702762</v>
+        <v>0.1500537991523743</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004359607584774494</v>
+        <v>0.7077879905700684</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001258351258002222</v>
+        <v>0.09119956940412521</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002703702310100198</v>
+        <v>0.1777288317680359</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003548448148649186</v>
+        <v>0.2011515647172928</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003830435685813427</v>
+        <v>0.594504714012146</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001831273693824187</v>
+        <v>0.007470754440873861</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.99216572381556e-05</v>
+        <v>0.1442095041275024</v>
       </c>
       <c r="R7" t="n">
-        <v>4.323141183704138e-05</v>
+        <v>0.01286953687667847</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003156091552227736</v>
+        <v>0.03507441282272339</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008452613255940378</v>
+        <v>0.0436505563557148</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001827364612836391</v>
+        <v>0.1067719310522079</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002909932809416205</v>
+        <v>0.07950052618980408</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001389061944792047</v>
+        <v>0.08220314979553223</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002109068154823035</v>
+        <v>0.1244202926754951</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000591768475715071</v>
+        <v>0.08455131947994232</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0004975750343874097</v>
+        <v>0.1113131642341614</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003106602234765887</v>
+        <v>0.01681189239025116</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002320258063264191</v>
+        <v>0.04675117880105972</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0008208799990825355</v>
+        <v>0.1380881071090698</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.868028089636937e-06</v>
+        <v>0.04921559616923332</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.86857393803075e-05</v>
+        <v>0.1878565102815628</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0002756394678726792</v>
+        <v>0.103634811937809</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0005111091304570436</v>
+        <v>0.08848480880260468</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0004567177384160459</v>
+        <v>0.06163059920072556</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003751192707568407</v>
+        <v>0.3142645359039307</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7.465600356226787e-05</v>
+        <v>0.06501495838165283</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0004483814700506628</v>
+        <v>0.02837705053389072</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.000770194863434881</v>
+        <v>0.1276603192090988</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001865111698862165</v>
+        <v>0.071747787296772</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0003407878102734685</v>
+        <v>0.01837611943483353</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.000429260078817606</v>
+        <v>0.01444121636450291</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0009431141661480069</v>
+        <v>0.122531421482563</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0003084807540290058</v>
+        <v>0.1186356246471405</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0002560403081588447</v>
+        <v>0.2107737064361572</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0007001372869126499</v>
+        <v>0.04346465691924095</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0002881358959712088</v>
+        <v>0.09899810701608658</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.003248512744903564</v>
+        <v>0.6698195934295654</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0001424910296918824</v>
+        <v>0.1055168360471725</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0003598197363317013</v>
+        <v>0.0642198771238327</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0003205767134204507</v>
+        <v>0.2424086928367615</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.002127486979588866</v>
+        <v>0.3460693061351776</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.686141669983044e-05</v>
+        <v>0.01311020180583</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.000841984641738236</v>
+        <v>0.01325245294719934</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0005952664650976658</v>
+        <v>0.0411481186747551</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0003002729208674282</v>
+        <v>0.01064709573984146</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.001073725055903196</v>
+        <v>0.002684084698557854</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.001511114998720586</v>
+        <v>0.1451615989208221</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001088307588361204</v>
+        <v>0.09266278892755508</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001586942700669169</v>
+        <v>0.03345952555537224</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.001235270174220204</v>
+        <v>0.1752773970365524</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0001446175738237798</v>
+        <v>0.05288704112172127</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.00122055143583566</v>
+        <v>0.1221269592642784</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.145631540566683e-05</v>
+        <v>0.05500370636582375</v>
       </c>
       <c r="BL7" t="n">
-        <v>6.486425263574347e-05</v>
+        <v>0.05929004400968552</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0005903513520024717</v>
+        <v>0.1592837572097778</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0007258234545588493</v>
+        <v>0.02753472328186035</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0007028458639979362</v>
+        <v>0.05098658055067062</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.72607823414728e-05</v>
+        <v>0.08744075149297714</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.207033245824277e-05</v>
+        <v>0.07601483166217804</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0003953538544010371</v>
+        <v>0.2105922847986221</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0001784444320946932</v>
+        <v>0.03810438886284828</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002545000752434134</v>
+        <v>0.04769951850175858</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0001724618778098375</v>
+        <v>0.02260309085249901</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.001671078847721219</v>
+        <v>0.3756685554981232</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0008711108239367604</v>
+        <v>0.1005450114607811</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0002490000042598695</v>
+        <v>0.07781311124563217</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0002153939567506313</v>
+        <v>0.1082319468259811</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0007601281977258623</v>
+        <v>0.2719557285308838</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0003952897095587105</v>
+        <v>0.1525863111019135</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0004764512996189296</v>
+        <v>0.06019037216901779</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0005048811435699463</v>
+        <v>0.01479738391935825</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.000035263132304e-05</v>
+        <v>0.0215317327529192</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0009455282706767321</v>
+        <v>0.1940545737743378</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.000592881056945771</v>
+        <v>0.007201519794762135</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0004996589850634336</v>
+        <v>0.01921287924051285</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004309132636990398</v>
+        <v>0.004327744245529175</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0004645654116757214</v>
+        <v>0.1557004451751709</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0003188833361491561</v>
+        <v>0.0458049438893795</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.00026352220447734</v>
+        <v>0.06026748195290565</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0003000804572366178</v>
+        <v>0.02492807991802692</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0007120485533960164</v>
+        <v>0.1488205790519714</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.000291433825623244</v>
+        <v>0.3615516424179077</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0002030940377153456</v>
+        <v>0.2210437059402466</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0008897038642317057</v>
+        <v>0.2083471715450287</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0001840076438384131</v>
+        <v>0.1431207209825516</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0001391856203554198</v>
+        <v>0.1418138891458511</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0008195481495931745</v>
+        <v>0.02165679633617401</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0009448987548239529</v>
+        <v>0.01311721559613943</v>
       </c>
       <c r="CU7" t="n">
-        <v>5.584691098192707e-05</v>
+        <v>0.06044139713048935</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.863005986204371e-05</v>
+        <v>0.01775032840669155</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0008315527229569852</v>
+        <v>0.1782297194004059</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0006369845941662788</v>
+        <v>0.03194376826286316</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0007505335961468518</v>
+        <v>0.0392335020005703</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.000391747074900195</v>
+        <v>0.001676280051469803</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0005760767962783575</v>
+        <v>0.1497347801923752</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0002818909124471247</v>
+        <v>0.02813735045492649</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0004792202380485833</v>
+        <v>0.03378823772072792</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0002410369925200939</v>
+        <v>0.01839533448219299</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0005280007026158273</v>
+        <v>0.1410394757986069</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.000814757018815726</v>
+        <v>0.09046649187803268</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0002229664678452536</v>
+        <v>0.1212089508771896</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001086656237021089</v>
+        <v>0.1229555085301399</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0004529068828560412</v>
+        <v>0.1417426466941833</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0001406503724865615</v>
+        <v>0.1309118866920471</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0004297831910662353</v>
+        <v>0.04233355075120926</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0009681358933448792</v>
+        <v>0.09198064357042313</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0004201918200124055</v>
+        <v>0.09394149482250214</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0003176536411046982</v>
+        <v>0.04043756797909737</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0002016305952565745</v>
+        <v>0.09734734892845154</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0004196849185973406</v>
+        <v>0.05266779661178589</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0005336985923349857</v>
+        <v>0.03494836390018463</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.797629223205149e-05</v>
+        <v>0.03078434616327286</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0002244183851871639</v>
+        <v>0.06210782006382942</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0001360218884656206</v>
+        <v>0.007703671231865883</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.760437200777233e-05</v>
+        <v>0.0653572753071785</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0007167299627326429</v>
+        <v>0.02927909977734089</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002725414815358818</v>
+        <v>0.05806422233581543</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0005189990624785423</v>
+        <v>0.05338804423809052</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0008164605824276805</v>
+        <v>0.02783508598804474</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0005064899451099336</v>
+        <v>0.01189342979341745</v>
       </c>
       <c r="EA7" t="n">
-        <v>5.532059003598988e-05</v>
+        <v>0.02659597806632519</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.980865974677727e-05</v>
+        <v>0.01037001051008701</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.842028672806919e-05</v>
+        <v>0.03800090402364731</v>
       </c>
       <c r="ED7" t="n">
-        <v>6.054418918211013e-06</v>
+        <v>0.03433413431048393</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0001143270637840033</v>
+        <v>0.1871718466281891</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0003305658174213022</v>
+        <v>0.009738792665302753</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0006608064286410809</v>
+        <v>0.03864812850952148</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0004008611140307039</v>
+        <v>0.04348500818014145</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.00016533795860596</v>
+        <v>0.01088005024939775</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001769423543009907</v>
+        <v>0.06942303478717804</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0003486078639980406</v>
+        <v>0.1400718092918396</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0005475196521729231</v>
+        <v>0.01013922318816185</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0001073877938324586</v>
+        <v>0.007506352849304676</v>
       </c>
       <c r="EN7" t="n">
-        <v>4.440975317265838e-06</v>
+        <v>0.01144309528172016</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.679082924965769e-05</v>
+        <v>0.01401694025844336</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0005362826632335782</v>
+        <v>0.09747777879238129</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0008581375586800277</v>
+        <v>0.08287890255451202</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0006162350764498115</v>
+        <v>0.01512298732995987</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.000159377625095658</v>
+        <v>0.09229616820812225</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.00013738326379098</v>
+        <v>0.08783749490976334</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0003128411190118641</v>
+        <v>0.01985648646950722</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0007309893262572587</v>
+        <v>0.00168164074420929</v>
       </c>
       <c r="EW7" t="n">
-        <v>8.378570782952011e-05</v>
+        <v>0.03609151765704155</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001155696663772687</v>
+        <v>0.008858911693096161</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0008359135827049613</v>
+        <v>0.212612584233284</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0004763790930155665</v>
+        <v>0.01731985062360764</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0005238561425358057</v>
+        <v>0.03070257790386677</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0004748701176140457</v>
+        <v>0.02697386592626572</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0004803359624929726</v>
+        <v>0.1441789418458939</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0004179695970378816</v>
+        <v>0.04354230687022209</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0002600525040179491</v>
+        <v>0.0513816699385643</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0004425276420079172</v>
+        <v>0.01136952079832554</v>
       </c>
       <c r="FG7" t="n">
-        <v>6.849176133982837e-05</v>
+        <v>0.03046954795718193</v>
       </c>
       <c r="FH7" t="n">
-        <v>9.253920143237337e-05</v>
+        <v>0.1775069534778595</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0007525112014263868</v>
+        <v>0.0787983238697052</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.00104863871820271</v>
+        <v>0.1271039992570877</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0002530571073293686</v>
+        <v>0.09775085002183914</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0007304495666176081</v>
+        <v>0.1481238901615143</v>
       </c>
       <c r="FM7" t="n">
-        <v>5.281782796373591e-05</v>
+        <v>0.06803569942712784</v>
       </c>
       <c r="FN7" t="n">
-        <v>7.494020974263549e-05</v>
+        <v>0.2021049857139587</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0002815353800542653</v>
+        <v>0.15545254945755</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0002921879640780389</v>
+        <v>0.1182961240410805</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0008766732062213123</v>
+        <v>0.1889792680740356</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0002796821354422718</v>
+        <v>0.03897024691104889</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0006133215501904488</v>
+        <v>0.1441728472709656</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0006705217529088259</v>
+        <v>0.08785439282655716</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.000788917881436646</v>
+        <v>0.1437649875879288</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0001555499038659036</v>
+        <v>0.04463790729641914</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0004703744780272245</v>
+        <v>0.09251853078603745</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0004031779535580426</v>
+        <v>0.02670592814683914</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0009891698136925697</v>
+        <v>0.1057809293270111</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0002747506077867001</v>
+        <v>0.0278920866549015</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0002275003062095493</v>
+        <v>0.1193079277873039</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0001431439304724336</v>
+        <v>0.0430731326341629</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0002646393259055912</v>
+        <v>0.2253033369779587</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0007322257151827216</v>
+        <v>0.09459882974624634</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.002133396686986089</v>
+        <v>0.07246894389390945</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.109717752318829e-05</v>
+        <v>0.01889535412192345</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0006045689224265516</v>
+        <v>0.01574991270899773</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.001492217415943742</v>
+        <v>0.1242296993732452</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06141118332743645</v>
+        <v>0.108103334903717</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005195898469537497</v>
+        <v>0.06179196760058403</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03715737536549568</v>
+        <v>0.4322636127471924</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00749159837141633</v>
+        <v>0.08057861030101776</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002337113255634904</v>
+        <v>0.2762811183929443</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002902262611314654</v>
+        <v>0.1921277940273285</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003774398239329457</v>
+        <v>0.1325771361589432</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00386641570366919</v>
+        <v>0.054383285343647</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002054499462246895</v>
+        <v>0.1416840106248856</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05128977447748184</v>
+        <v>0.05442233383655548</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004049786366522312</v>
+        <v>0.08093468844890594</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03093627467751503</v>
+        <v>0.556786060333252</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01543122529983521</v>
+        <v>0.03672634810209274</v>
       </c>
       <c r="O8" t="n">
-        <v>0.004331117030233145</v>
+        <v>0.2839618027210236</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004354381002485752</v>
+        <v>0.1893922537565231</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008370713330805302</v>
+        <v>0.04007929563522339</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005532014649361372</v>
+        <v>0.1261734962463379</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003491620300337672</v>
+        <v>0.008806448429822922</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009649083018302917</v>
+        <v>0.01515616569668055</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008575065061450005</v>
+        <v>0.01927227526903152</v>
       </c>
       <c r="V8" t="n">
-        <v>2.419925294816494e-05</v>
+        <v>0.01397068798542023</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01584244146943092</v>
+        <v>0.04551307857036591</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01489332504570484</v>
+        <v>0.128562867641449</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.006888458970934153</v>
+        <v>0.01312272809445858</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004604827146977186</v>
+        <v>0.01577024906873703</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0004619533428922296</v>
+        <v>0.01884513907134533</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.008940123952925205</v>
+        <v>0.007218494545668364</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01258284784853458</v>
+        <v>0.02579959109425545</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.003943718504160643</v>
+        <v>0.03224529698491096</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002111999318003654</v>
+        <v>0.06470693647861481</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004326797556132078</v>
+        <v>0.05600008368492126</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004512576851993799</v>
+        <v>0.1566310524940491</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002002916298806667</v>
+        <v>0.06527966260910034</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.004188451915979385</v>
+        <v>0.06628828495740891</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0023489142768085</v>
+        <v>0.0863315686583519</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.00337179796770215</v>
+        <v>0.03201717883348465</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001667108037509024</v>
+        <v>0.03860480710864067</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.003452707314863801</v>
+        <v>0.007900487631559372</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0003461504820734262</v>
+        <v>0.05096971243619919</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.007728902157396078</v>
+        <v>0.08639051020145416</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.005235630087554455</v>
+        <v>0.08787289261817932</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.006981991231441498</v>
+        <v>0.06489810347557068</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00434020534157753</v>
+        <v>0.05574502795934677</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.00194026343524456</v>
+        <v>0.03075877577066422</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001605546800419688</v>
+        <v>0.07943280041217804</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03931888937950134</v>
+        <v>0.1085943430662155</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.004768571816384792</v>
+        <v>0.1245815604925156</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01646466925740242</v>
+        <v>0.1760458797216415</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.003695596475154161</v>
+        <v>0.2555766999721527</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.007160502951592207</v>
+        <v>0.2054322957992554</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0004716683179140091</v>
+        <v>0.01259718928486109</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.006267281249165535</v>
+        <v>0.003884694306179881</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01240020897239447</v>
+        <v>0.119803711771965</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.007848167791962624</v>
+        <v>0.0220735277980566</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02022583223879337</v>
+        <v>0.02276978641748428</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.01563112065196037</v>
+        <v>0.04252380132675171</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.008054526522755623</v>
+        <v>0.003957897424697876</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.007995438762009144</v>
+        <v>0.1652617454528809</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.01354616694152355</v>
+        <v>0.003059159033000469</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.003736509475857019</v>
+        <v>0.07374605536460876</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002424133010208607</v>
+        <v>0.03823645040392876</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.007368113845586777</v>
+        <v>0.06145559996366501</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.01206213142722845</v>
+        <v>0.02121594175696373</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.01176353357732296</v>
+        <v>0.01877941936254501</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.01072447467595339</v>
+        <v>0.005836237221956253</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.000247470336034894</v>
+        <v>0.06267020106315613</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.00994545966386795</v>
+        <v>0.06800015270709991</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.008364353328943253</v>
+        <v>0.0332922451198101</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.01051390916109085</v>
+        <v>0.0228709951043129</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.00235514366067946</v>
+        <v>0.007006283849477768</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.003347245510667562</v>
+        <v>0.0220651887357235</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002055772580206394</v>
+        <v>0.05696845054626465</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01925359480082989</v>
+        <v>0.06111746281385422</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.006354208569973707</v>
+        <v>0.04663759097456932</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.004956240765750408</v>
+        <v>0.1606801897287369</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.01211312413215637</v>
+        <v>0.04553389549255371</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01423626951873302</v>
+        <v>0.1286851465702057</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0006691340240649879</v>
+        <v>0.0302866343408823</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.002508273813873529</v>
+        <v>0.02468374744057655</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003630886320024729</v>
+        <v>0.02323559299111366</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.805719411000609e-05</v>
+        <v>0.08198116719722748</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.009164598770439625</v>
+        <v>0.0396532230079174</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.00139573379419744</v>
+        <v>0.02392040751874447</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004353998228907585</v>
+        <v>0.134043350815773</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002903156680986285</v>
+        <v>0.005536534823477268</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001503052655607462</v>
+        <v>0.01240357011556625</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0001321494928561151</v>
+        <v>0.01024539582431316</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00031275674700737</v>
+        <v>0.06287823617458344</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002797595923766494</v>
+        <v>0.01660356298089027</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.01076151430606842</v>
+        <v>0.132420152425766</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01005209237337112</v>
+        <v>0.01705659553408623</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.003514619078487158</v>
+        <v>0.1519549787044525</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.003270053304731846</v>
+        <v>0.1486515402793884</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01947082579135895</v>
+        <v>0.07844981551170349</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.003999004606157541</v>
+        <v>0.07618707418441772</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.003149450290948153</v>
+        <v>0.0620303675532341</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.01210180856287479</v>
+        <v>0.0186971090734005</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.007361936382949352</v>
+        <v>0.001167227514088154</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001101552392356098</v>
+        <v>0.08516915142536163</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.008059109561145306</v>
+        <v>0.0349738597869873</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.004306882619857788</v>
+        <v>0.03527681902050972</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.005697420798242092</v>
+        <v>0.1442020237445831</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.00359453889541328</v>
+        <v>0.01767650991678238</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.001566527411341667</v>
+        <v>0.01601017452776432</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001393858576193452</v>
+        <v>0.0009405305609107018</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.00161208538338542</v>
+        <v>0.04147545248270035</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.002935906173661351</v>
+        <v>0.0204892847687006</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.009877731092274189</v>
+        <v>0.07428212463855743</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.009910945780575275</v>
+        <v>0.02449467033147812</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.003856340423226357</v>
+        <v>0.01447346061468124</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.02734320797026157</v>
+        <v>0.1307210922241211</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01755331829190254</v>
+        <v>0.0252319797873497</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.004076657351106405</v>
+        <v>0.126085177063942</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.000600817147642374</v>
+        <v>0.005701273679733276</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.006162485107779503</v>
+        <v>0.2359094172716141</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002792328596115112</v>
+        <v>0.07026661932468414</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.00308286165818572</v>
+        <v>0.07273180782794952</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.00382339209318161</v>
+        <v>0.03737274557352066</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.006700296420603991</v>
+        <v>0.009494811296463013</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.007006543688476086</v>
+        <v>0.04407120868563652</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01202583126723766</v>
+        <v>0.01682176254689693</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.00205498724244535</v>
+        <v>0.08189667761325836</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.004285512026399374</v>
+        <v>0.08086030185222626</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.002252403879538178</v>
+        <v>0.007203372195363045</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.002762964460998774</v>
+        <v>0.120911180973053</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.005192592740058899</v>
+        <v>0.01072385441511869</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01338915340602398</v>
+        <v>0.01390940975397825</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.004245482385158539</v>
+        <v>0.1178193986415863</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.007880088873207569</v>
+        <v>0.03601069748401642</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01142594218254089</v>
+        <v>0.0576917752623558</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.008569098077714443</v>
+        <v>0.05167479813098907</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.003233765717595816</v>
+        <v>0.05233252048492432</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.002904941560700536</v>
+        <v>0.1095556542277336</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.007573619484901428</v>
+        <v>0.13168004155159</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.002611005678772926</v>
+        <v>0.08315910398960114</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.004741185810416937</v>
+        <v>0.03000825271010399</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002732226275838912</v>
+        <v>0.02917913533747196</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.01019761804491282</v>
+        <v>0.1366017162799835</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.008026683703064919</v>
+        <v>0.02171282097697258</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.008791954256594181</v>
+        <v>0.01185646932572126</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001572265522554517</v>
+        <v>0.001918184570968151</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.001723205437883735</v>
+        <v>0.04141407459974289</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001888876198790967</v>
+        <v>0.008425373584032059</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.002959370147436857</v>
+        <v>0.05980014428496361</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.006936350837349892</v>
+        <v>0.03949815034866333</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.004932137671858072</v>
+        <v>0.07315181195735931</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.002762832678854465</v>
+        <v>0.1381265819072723</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.001041056704707444</v>
+        <v>0.001198736950755119</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.00322937942110002</v>
+        <v>0.1076465398073196</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.009874382056295872</v>
+        <v>0.07856058329343796</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.007909007370471954</v>
+        <v>0.02699463069438934</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.002331312280148268</v>
+        <v>0.141597718000412</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.001671081059612334</v>
+        <v>0.08950010687112808</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.008854778483510017</v>
+        <v>0.04851836711168289</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001336920540779829</v>
+        <v>0.0174054317176342</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00520284753292799</v>
+        <v>0.1597160995006561</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.001004275865852833</v>
+        <v>0.006963429972529411</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.003641563234850764</v>
+        <v>0.03016618266701698</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.003284891834482551</v>
+        <v>0.01130937226116657</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001810481073334813</v>
+        <v>0.05089996755123138</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.002833608537912369</v>
+        <v>0.01357615739107132</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001172917982330546</v>
+        <v>0.001907785423099995</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.008433999493718147</v>
+        <v>0.01219688355922699</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.002223185729235411</v>
+        <v>0.0830821767449379</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.002268261276185513</v>
+        <v>0.0392458513379097</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00790716428309679</v>
+        <v>0.06891138106584549</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.005254452582448721</v>
+        <v>0.06996753811836243</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.005650383420288563</v>
+        <v>0.03474594280123711</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.001304123783484101</v>
+        <v>0.01639369688928127</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.000529960379935801</v>
+        <v>0.0688900351524353</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0009603322250768542</v>
+        <v>0.004110043868422508</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01122317649424076</v>
+        <v>0.0814121812582016</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.002432366367429495</v>
+        <v>0.03621292114257812</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.005366850644350052</v>
+        <v>0.0636812299489975</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.008290667086839676</v>
+        <v>0.03087155520915985</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.01339748408645391</v>
+        <v>0.08358313888311386</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.006935208104550838</v>
+        <v>0.01187828928232193</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.005360875278711319</v>
+        <v>0.2044841051101685</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.003627895843237638</v>
+        <v>0.01894280314445496</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.004341109655797482</v>
+        <v>0.04540929198265076</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.005048679187893867</v>
+        <v>0.008170116692781448</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.007728620897978544</v>
+        <v>0.08632754534482956</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.004121941514313221</v>
+        <v>0.1802164018154144</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.002794068306684494</v>
+        <v>0.1243041604757309</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01188437454402447</v>
+        <v>0.0720345750451088</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.001695576123893261</v>
+        <v>0.1333675384521484</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.004237744491547346</v>
+        <v>0.007882386445999146</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0010392633266747</v>
+        <v>0.1017353683710098</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.007040469441562891</v>
+        <v>0.01524291001260281</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002198024187237024</v>
+        <v>0.009311545640230179</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001983932452276349</v>
+        <v>0.006689277477562428</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002644534688442945</v>
+        <v>0.08065454661846161</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00020284453057684</v>
+        <v>0.03436290845274925</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0017342270584777</v>
+        <v>0.007475047372281551</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0006570451660081744</v>
+        <v>0.03239282220602036</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0008653479744680226</v>
+        <v>0.0007899893098510802</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002797546912916005</v>
+        <v>0.002338365651667118</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006333510391414165</v>
+        <v>0.003669267054647207</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001699474058113992</v>
+        <v>0.003057271242141724</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001826588530093431</v>
+        <v>0.00826300960034132</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0006162280915305018</v>
+        <v>0.1086867302656174</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001618139212951064</v>
+        <v>0.0152190774679184</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002548703923821449</v>
+        <v>0.01959468983113766</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002565367321949452</v>
+        <v>0.02984845079481602</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0002348394191358238</v>
+        <v>0.0229641031473875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0007992688333615661</v>
+        <v>0.004066442139446735</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0006981713813729584</v>
+        <v>0.008766631595790386</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001451807329431176</v>
+        <v>0.004839911125600338</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0007382514304481447</v>
+        <v>0.002765089273452759</v>
       </c>
       <c r="V9" t="n">
-        <v>2.843697438947856e-05</v>
+        <v>0.01321237906813622</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0005648619262501597</v>
+        <v>0.0009105998324230313</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0007792323594912887</v>
+        <v>0.02264608629047871</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0003725070564541966</v>
+        <v>0.002053492702543736</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001051302184350789</v>
+        <v>0.002954124007374048</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.741308268625289e-05</v>
+        <v>0.00174609397072345</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000499385641887784</v>
+        <v>0.0005330438725650311</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001511045615188777</v>
+        <v>0.008951267227530479</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0003664669638965279</v>
+        <v>0.003796896897256374</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001062576309777796</v>
+        <v>0.009642721153795719</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0007452027057297528</v>
+        <v>0.03626396507024765</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001308550708927214</v>
+        <v>0.0187232680618763</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0003937272704206407</v>
+        <v>0.01188855059444904</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0006324925925582647</v>
+        <v>0.01457200571894646</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0006433599046431482</v>
+        <v>0.02082696184515953</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0009453910170122981</v>
+        <v>0.01348545402288437</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0003253890026826411</v>
+        <v>0.01159202307462692</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0001065142860170454</v>
+        <v>0.007721253205090761</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0005086837918497622</v>
+        <v>0.01977199502289295</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001095275045372546</v>
+        <v>0.01337902061641216</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0002759089693427086</v>
+        <v>0.006382142659276724</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0005900561227463186</v>
+        <v>0.01759973168373108</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0009428209159523249</v>
+        <v>0.00568724051117897</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0003244678373448551</v>
+        <v>0.0002544187009334564</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.004337341990321875</v>
+        <v>0.004101341590285301</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0007821733597666025</v>
+        <v>0.0005981877911835909</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00162606593221426</v>
+        <v>0.004828325472772121</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001252342597581446</v>
+        <v>0.05584147572517395</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0009083238546736538</v>
+        <v>0.00458183791488409</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.134191501885653e-07</v>
+        <v>0.005043884739279747</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0002501757116988301</v>
+        <v>0.011492520570755</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0008426578715443611</v>
+        <v>0.00831938162446022</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0006776867667213082</v>
+        <v>0.01056945882737637</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.002876691753044724</v>
+        <v>0.01070766896009445</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.003371883416548371</v>
+        <v>0.005475068464875221</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.973879787139595e-05</v>
+        <v>0.000437485461588949</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.286848030053079e-05</v>
+        <v>0.02276260033249855</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001066676457412541</v>
+        <v>0.02675455436110497</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.614555943291634e-05</v>
+        <v>0.01048573944717646</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0006980560719966888</v>
+        <v>0.02264176309108734</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.001625736942514777</v>
+        <v>0.00120045430958271</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001472354982979596</v>
+        <v>0.02846099436283112</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001841400953708217</v>
+        <v>0.003662315662950277</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0008966429159045219</v>
+        <v>0.01290951482951641</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0004160010139457881</v>
+        <v>0.007068650797009468</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.000641112623270601</v>
+        <v>0.006204200908541679</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0007231786148622632</v>
+        <v>0.01100676972419024</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0004318511346355081</v>
+        <v>0.00155098270624876</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00043324357829988</v>
+        <v>0.0009239855571649969</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0007332696695812047</v>
+        <v>0.004550875630229712</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0005633941618725657</v>
+        <v>0.01072437223047018</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001729521551169455</v>
+        <v>0.001652023755013943</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0003938778536394238</v>
+        <v>0.01015770528465509</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0008109319023787975</v>
+        <v>0.000283227302134037</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.000251331424806267</v>
+        <v>0.05622380971908569</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0002204359479947016</v>
+        <v>0.00734153063967824</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.158502345788293e-05</v>
+        <v>0.0147211505100131</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.000363547820597887</v>
+        <v>0.005292151123285294</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0008074590004980564</v>
+        <v>0.001466132118366659</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0005621557938866317</v>
+        <v>0.003940856084227562</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001295944093726575</v>
+        <v>0.005412728060036898</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0006882492452859879</v>
+        <v>0.004431737121194601</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0002177119167754427</v>
+        <v>0.001071842620149255</v>
       </c>
       <c r="CG9" t="n">
-        <v>1.485976463300176e-05</v>
+        <v>0.02683036029338837</v>
       </c>
       <c r="CH9" t="n">
-        <v>7.704421295784414e-05</v>
+        <v>0.004558594897389412</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0008846988785080612</v>
+        <v>0.007525825407356024</v>
       </c>
       <c r="CJ9" t="n">
-        <v>4.293043457437307e-05</v>
+        <v>0.001060238340869546</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0008209269144572318</v>
+        <v>0.007997341454029083</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.000181087656528689</v>
+        <v>0.001936498912982643</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001454112585633993</v>
+        <v>0.003253471571952105</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0009636900504119694</v>
+        <v>0.02368290163576603</v>
       </c>
       <c r="CO9" t="n">
-        <v>4.594276833813637e-05</v>
+        <v>0.01495462842285633</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001248927321285009</v>
+        <v>0.04177742451429367</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001342690899036825</v>
+        <v>0.009937192313373089</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0004151472239755094</v>
+        <v>0.009970881976187229</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001193352160044014</v>
+        <v>0.008108686655759811</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001596433809027076</v>
+        <v>0.01276578102260828</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.000356188218574971</v>
+        <v>0.02358620427548885</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.001082137459889054</v>
+        <v>0.004126403480768204</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0006978792953304946</v>
+        <v>0.004163424484431744</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0002704462385736406</v>
+        <v>0.001053289161063731</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001414811849826947</v>
+        <v>0.02707821317017078</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.29709032989922e-05</v>
+        <v>0.001313728280365467</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0008306073723360896</v>
+        <v>0.00587479816749692</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001152207332779653</v>
+        <v>0.003485247492790222</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0005656885914504528</v>
+        <v>0.008192621171474457</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0002078521793009713</v>
+        <v>0.0002963230945169926</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0003729824675247073</v>
+        <v>0.007401986047625542</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001581541378982365</v>
+        <v>0.002261297777295113</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.002537909895181656</v>
+        <v>0.00614208122715354</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002192476531490684</v>
+        <v>0.01966746896505356</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001988507574424148</v>
+        <v>0.00786903128027916</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001590725150890648</v>
+        <v>0.009956779889762402</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.53162894397974e-05</v>
+        <v>0.008619649335741997</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.002479513641446829</v>
+        <v>0.04357388615608215</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0008342572255060077</v>
+        <v>0.004572316072881222</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0006335555226542056</v>
+        <v>0.007959775626659393</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001523023238405585</v>
+        <v>0.01164452265948057</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0007111825980246067</v>
+        <v>0.01665372028946877</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0007670553168281913</v>
+        <v>0.008993301540613174</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0009105283534154296</v>
+        <v>0.004075119271874428</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0001959089131560177</v>
+        <v>0.004545448813587427</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0003152764402329922</v>
+        <v>0.0008564343443140388</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0002663782215677202</v>
+        <v>0.001177174039185047</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0007209473988041282</v>
+        <v>0.02568847313523293</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0009324317798018456</v>
+        <v>0.00270260008983314</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0004065676766913384</v>
+        <v>0.003413322381675243</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0004502876254264265</v>
+        <v>0.03102209977805614</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0002580896252766252</v>
+        <v>0.01091310847550631</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0007542463717982173</v>
+        <v>0.01146023999899626</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0003207573317922652</v>
+        <v>0.01198004279285669</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.826248990255408e-05</v>
+        <v>0.008311765268445015</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001556095667183399</v>
+        <v>0.03138960897922516</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003996967570856214</v>
+        <v>0.02127230726182461</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001440238556824625</v>
+        <v>0.01099102664738894</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001086921198293567</v>
+        <v>0.006170873064547777</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0009385136654600501</v>
+        <v>0.0006757888477295637</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001023730030283332</v>
+        <v>0.0239940881729126</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0007557367207482457</v>
+        <v>0.009066300466656685</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0004639158141799271</v>
+        <v>0.007822338491678238</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001308625796809793</v>
+        <v>0.005496418103575706</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0002523816074244678</v>
+        <v>0.003665575059130788</v>
       </c>
       <c r="EN9" t="n">
-        <v>2.04186490009306e-05</v>
+        <v>0.0006905632326379418</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0002562947920523584</v>
+        <v>0.002813200000673532</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001439075800590217</v>
+        <v>0.003111496334895492</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0003155049926135689</v>
+        <v>0.005377467256039381</v>
       </c>
       <c r="ER9" t="n">
-        <v>8.434147457592189e-05</v>
+        <v>0.03157408535480499</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0003198157646693289</v>
+        <v>0.0001689986092969775</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0009720606030896306</v>
+        <v>0.0243160855025053</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0005898870876990259</v>
+        <v>0.009690048173069954</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0005601201555691659</v>
+        <v>0.009982774034142494</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.001375688822008669</v>
+        <v>0.01090090163052082</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.001048109028488398</v>
+        <v>0.003895720466971397</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0007114580948837101</v>
+        <v>0.002147240098565817</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0004699596902355552</v>
+        <v>0.001683529233559966</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001370733079966158</v>
+        <v>0.03470370545983315</v>
       </c>
       <c r="FB9" t="n">
-        <v>5.096227323519997e-05</v>
+        <v>0.005022409372031689</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0006458154530264437</v>
+        <v>0.001343096257187426</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0001147928051068448</v>
+        <v>0.003218669444322586</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0006972355186007917</v>
+        <v>0.01015455741435289</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0002235811552964151</v>
+        <v>0.0005694772116839886</v>
       </c>
       <c r="FG9" t="n">
-        <v>1.107054413296282e-05</v>
+        <v>0.003958816640079021</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001096465508453548</v>
+        <v>0.00176907260902226</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.001317970105446875</v>
+        <v>0.008666460402309895</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.000352958682924509</v>
+        <v>0.005282999016344547</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0003857211559079587</v>
+        <v>0.01282049715518951</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.001150567783042789</v>
+        <v>0.0001743034226819873</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.000428030441980809</v>
+        <v>0.0003351061604917049</v>
       </c>
       <c r="FN9" t="n">
-        <v>7.773711695335805e-05</v>
+        <v>0.0131454411894083</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0003548974345903844</v>
+        <v>0.009305542334914207</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001008267747238278</v>
+        <v>0.004801747389137745</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.001834410824812949</v>
+        <v>0.00701356865465641</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.001074183615855873</v>
+        <v>0.003211227944120765</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.001028719008900225</v>
+        <v>0.02702713757753372</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0005168380448594689</v>
+        <v>0.003550565335899591</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.001174465985968709</v>
+        <v>0.0140311811119318</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0003455498372204602</v>
+        <v>0.0101663414388895</v>
       </c>
       <c r="FW9" t="n">
-        <v>4.21143340645358e-05</v>
+        <v>0.01111651677638292</v>
       </c>
       <c r="FX9" t="n">
-        <v>7.849841495044529e-06</v>
+        <v>0.005283087026327848</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0004629850445780903</v>
+        <v>0.003816060489043593</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0006379308179020882</v>
+        <v>0.005431793164461851</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0001387150259688497</v>
+        <v>0.004652975127100945</v>
       </c>
       <c r="GB9" t="n">
-        <v>5.493056960403919e-05</v>
+        <v>0.04048977792263031</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.001423957059159875</v>
+        <v>0.001169146504253149</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0002654232084751129</v>
+        <v>0.006062823347747326</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0008902635308913887</v>
+        <v>0.02249002270400524</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0002179228322347626</v>
+        <v>0.00280400924384594</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0004533740575425327</v>
+        <v>0.001934863394126296</v>
       </c>
     </row>
     <row r="10">
@@ -6689,2847 +6689,2847 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.226001121627633e-06</v>
+        <v>1.409921281947391e-07</v>
       </c>
       <c r="B12" t="n">
-        <v>3.573562571546063e-05</v>
+        <v>3.5069672321697e-07</v>
       </c>
       <c r="C12" t="n">
-        <v>3.944978743675165e-06</v>
+        <v>1.367142488106765e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>2.661719372554217e-05</v>
+        <v>1.742590995945648e-07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.04664368336671e-05</v>
+        <v>6.23207796479619e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>5.296995368553326e-06</v>
+        <v>1.324705323213493e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>1.618670012248913e-06</v>
+        <v>7.954621850103649e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>1.435504941582622e-06</v>
+        <v>7.595193096676667e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>1.559038196319307e-06</v>
+        <v>7.142453739561461e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>7.473211553588044e-06</v>
+        <v>4.265969266725733e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>2.800857146212365e-05</v>
+        <v>3.763238964893389e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>2.96085590889561e-06</v>
+        <v>1.727079990132552e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>2.024856075877324e-05</v>
+        <v>2.747510166045686e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.372718725178856e-05</v>
+        <v>1.754751366433993e-07</v>
       </c>
       <c r="O12" t="n">
-        <v>1.578175215399824e-05</v>
+        <v>1.467286523393341e-07</v>
       </c>
       <c r="P12" t="n">
-        <v>3.447196604611236e-06</v>
+        <v>4.023219091209285e-08</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.165151146182325e-06</v>
+        <v>1.297496687868716e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>5.548450303649588e-07</v>
+        <v>2.088109596343202e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>5.405399861047044e-08</v>
+        <v>1.207130395641798e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>6.586144991160836e-06</v>
+        <v>9.622139529597007e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>7.798348633514252e-07</v>
+        <v>4.473100645441264e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>2.583586592663778e-06</v>
+        <v>2.191744030710652e-08</v>
       </c>
       <c r="W12" t="n">
-        <v>4.742286819237052e-06</v>
+        <v>2.867301063247396e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>4.213750798953697e-06</v>
+        <v>2.500393492255171e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.261078851821367e-06</v>
+        <v>8.923770167257317e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.446625785523793e-06</v>
+        <v>6.984384270936062e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.264959665713832e-06</v>
+        <v>2.018906997136583e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.652035734878154e-06</v>
+        <v>3.777992674258712e-08</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.553888174996246e-06</v>
+        <v>5.619326870487384e-08</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.229375922979671e-06</v>
+        <v>3.092412725891336e-08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.770948301782482e-06</v>
+        <v>1.142129377740275e-07</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.197009618816082e-06</v>
+        <v>9.623590813134797e-08</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.692684107496461e-07</v>
+        <v>1.529233486508019e-07</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.020142569061136e-06</v>
+        <v>1.995961618206366e-08</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.095011723213247e-06</v>
+        <v>1.067544772581641e-07</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.442778790940793e-07</v>
+        <v>1.256519421843905e-08</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.98963720726897e-06</v>
+        <v>3.159458827894923e-08</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.33542334374215e-06</v>
+        <v>6.860665990870984e-08</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.170989207821549e-06</v>
+        <v>6.286373377406562e-08</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.011420974667999e-06</v>
+        <v>8.085214631137205e-08</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.993979023813154e-06</v>
+        <v>1.306952768231895e-08</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.809745963844762e-07</v>
+        <v>1.249158554372798e-08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.433384335949086e-06</v>
+        <v>3.778690427225229e-08</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.499936161053483e-06</v>
+        <v>1.953635120344188e-08</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.340564378755516e-06</v>
+        <v>1.972527741145313e-08</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.622859256007359e-06</v>
+        <v>3.456141595137296e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.460584801156074e-05</v>
+        <v>2.625729962346668e-07</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.084377794948523e-06</v>
+        <v>9.030996039882666e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.641063919232693e-06</v>
+        <v>3.551907212795413e-08</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.799819126015791e-08</v>
+        <v>2.43728152327094e-07</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.270370830752654e-06</v>
+        <v>1.934591153940346e-07</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.105494432835258e-07</v>
+        <v>1.062837817755735e-09</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.47908609607839e-06</v>
+        <v>3.993235964117048e-08</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.775756456685485e-06</v>
+        <v>2.211589134049063e-08</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.230635007232195e-06</v>
+        <v>1.863289433856608e-08</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.888098379116855e-06</v>
+        <v>1.473258208761763e-07</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.113701273425249e-05</v>
+        <v>1.194906573687149e-08</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.57081102670054e-06</v>
+        <v>1.002481155865098e-07</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.247431555384537e-05</v>
+        <v>1.391394874872276e-07</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.750190444407053e-06</v>
+        <v>6.086744974709291e-08</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.958445065814885e-06</v>
+        <v>1.648324854386374e-08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.713053830433637e-06</v>
+        <v>9.028435243862987e-08</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.156882198458334e-07</v>
+        <v>2.054122560934957e-08</v>
       </c>
       <c r="BL12" t="n">
-        <v>5.731745659431908e-06</v>
+        <v>3.128530678964125e-08</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.70546581002418e-06</v>
+        <v>4.935198205657798e-08</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.115651790925767e-06</v>
+        <v>6.838373423079247e-09</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.135025281153503e-06</v>
+        <v>4.667806052793821e-08</v>
       </c>
       <c r="BP12" t="n">
-        <v>7.185369213402737e-06</v>
+        <v>1.144196701829969e-07</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.501665676390985e-06</v>
+        <v>9.452881144511593e-09</v>
       </c>
       <c r="BR12" t="n">
-        <v>1.37029132929456e-06</v>
+        <v>4.48012471565562e-08</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.366995992517332e-06</v>
+        <v>3.399195591669013e-08</v>
       </c>
       <c r="BT12" t="n">
-        <v>2.507136969143176e-06</v>
+        <v>2.559457357165229e-08</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.488035862479592e-07</v>
+        <v>9.036057235789485e-09</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.150045045505976e-05</v>
+        <v>1.297376002185047e-07</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.11708424508106e-06</v>
+        <v>4.393132968516511e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>3.16604155159439e-06</v>
+        <v>1.153673601095306e-08</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.83487139540739e-07</v>
+        <v>1.220811007840439e-09</v>
       </c>
       <c r="BZ12" t="n">
-        <v>9.331969295089948e-07</v>
+        <v>7.637966348283953e-08</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.74253454033169e-06</v>
+        <v>9.22195155794725e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>8.87016653905448e-07</v>
+        <v>4.587061397387515e-09</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.118869472018559e-06</v>
+        <v>8.728062717011653e-09</v>
       </c>
       <c r="CD12" t="n">
-        <v>6.324766843590623e-08</v>
+        <v>2.550199340589643e-08</v>
       </c>
       <c r="CE12" t="n">
-        <v>6.156745257612783e-06</v>
+        <v>1.114533105806004e-07</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.359392621860025e-06</v>
+        <v>1.377588043638411e-09</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.1074915821373e-06</v>
+        <v>5.915221734653642e-08</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.659525878494605e-06</v>
+        <v>3.793557823428273e-08</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.079126943499432e-06</v>
+        <v>4.027550559726478e-08</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.01361479210027e-06</v>
+        <v>1.616309930341231e-08</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.044462692334491e-06</v>
+        <v>3.821541305626397e-09</v>
       </c>
       <c r="CL12" t="n">
-        <v>3.018771622009808e-06</v>
+        <v>2.888195638206525e-08</v>
       </c>
       <c r="CM12" t="n">
-        <v>7.382335297734244e-06</v>
+        <v>1.332491592620499e-07</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.047217151357472e-07</v>
+        <v>2.054585337418757e-07</v>
       </c>
       <c r="CO12" t="n">
-        <v>2.010402113228338e-06</v>
+        <v>1.356750516379179e-07</v>
       </c>
       <c r="CP12" t="n">
-        <v>9.786524969968013e-06</v>
+        <v>5.667788371965798e-08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>6.742634923284641e-06</v>
+        <v>3.934312076125934e-08</v>
       </c>
       <c r="CR12" t="n">
-        <v>3.111179864845326e-07</v>
+        <v>3.166207207527805e-08</v>
       </c>
       <c r="CS12" t="n">
-        <v>6.653850959992269e-06</v>
+        <v>1.072073274599461e-07</v>
       </c>
       <c r="CT12" t="n">
-        <v>1.816933831833012e-06</v>
+        <v>1.776453473212314e-08</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.205331273013144e-06</v>
+        <v>2.606479654332361e-08</v>
       </c>
       <c r="CV12" t="n">
-        <v>5.869410415471066e-07</v>
+        <v>1.325979681610079e-08</v>
       </c>
       <c r="CW12" t="n">
-        <v>5.486540885613067e-06</v>
+        <v>1.002507161729227e-07</v>
       </c>
       <c r="CX12" t="n">
-        <v>3.14444218929566e-06</v>
+        <v>5.884408071921143e-09</v>
       </c>
       <c r="CY12" t="n">
-        <v>4.204407105135033e-06</v>
+        <v>7.345909125433536e-08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.344878566873376e-06</v>
+        <v>4.629014327406367e-08</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.709583895921241e-06</v>
+        <v>4.994708291405914e-08</v>
       </c>
       <c r="DB12" t="n">
-        <v>2.204614020229201e-06</v>
+        <v>2.851983360585564e-08</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.351279934169725e-06</v>
+        <v>1.313360620258663e-08</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.026928996201605e-06</v>
+        <v>2.195583270747647e-08</v>
       </c>
       <c r="DE12" t="n">
-        <v>5.294650691212155e-06</v>
+        <v>5.946048631244594e-08</v>
       </c>
       <c r="DF12" t="n">
-        <v>8.918359526433051e-07</v>
+        <v>2.973972001996117e-08</v>
       </c>
       <c r="DG12" t="n">
-        <v>9.375413355883211e-06</v>
+        <v>6.440838973276186e-09</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.568516017869115e-05</v>
+        <v>7.90304923725671e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>5.845507530466421e-06</v>
+        <v>6.220044213023357e-08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.615796458689147e-06</v>
+        <v>1.274305390097652e-07</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.209639660577523e-06</v>
+        <v>1.469048882540847e-08</v>
       </c>
       <c r="DL12" t="n">
-        <v>6.007282991049578e-06</v>
+        <v>1.179953130758804e-07</v>
       </c>
       <c r="DM12" t="n">
-        <v>2.105266275975737e-06</v>
+        <v>3.663060255121309e-08</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.051605750035378e-06</v>
+        <v>6.815886521849279e-09</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.877730255728238e-06</v>
+        <v>6.475063685229543e-08</v>
       </c>
       <c r="DP12" t="n">
-        <v>3.716492301464314e-06</v>
+        <v>2.933910892011227e-08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.656436421006219e-07</v>
+        <v>7.419430403388105e-08</v>
       </c>
       <c r="DR12" t="n">
-        <v>2.03959484679217e-06</v>
+        <v>2.763857764875866e-08</v>
       </c>
       <c r="DS12" t="n">
-        <v>2.100243818858871e-06</v>
+        <v>1.585472375609243e-08</v>
       </c>
       <c r="DT12" t="n">
-        <v>8.165966960405058e-07</v>
+        <v>4.795741759267003e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>1.954520172375851e-07</v>
+        <v>4.188806101979026e-08</v>
       </c>
       <c r="DV12" t="n">
-        <v>6.135021067166235e-06</v>
+        <v>2.76081202343903e-08</v>
       </c>
       <c r="DW12" t="n">
-        <v>7.144442406570306e-07</v>
+        <v>7.51860707026708e-09</v>
       </c>
       <c r="DX12" t="n">
-        <v>5.011323082726449e-06</v>
+        <v>8.309102383918798e-08</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.548344456154155e-06</v>
+        <v>4.20999306527392e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.567821179080056e-07</v>
+        <v>4.506211226384949e-08</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.536820718683884e-06</v>
+        <v>3.817356741819822e-08</v>
       </c>
       <c r="EB12" t="n">
-        <v>5.833295290358365e-06</v>
+        <v>3.762156808306827e-08</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.941858499776572e-06</v>
+        <v>2.417572808610657e-09</v>
       </c>
       <c r="ED12" t="n">
-        <v>4.858551392317167e-07</v>
+        <v>1.17284983502941e-07</v>
       </c>
       <c r="EE12" t="n">
-        <v>1.192577087749669e-06</v>
+        <v>4.497648831147671e-08</v>
       </c>
       <c r="EF12" t="n">
-        <v>1.672541884545353e-06</v>
+        <v>3.013481375546689e-08</v>
       </c>
       <c r="EG12" t="n">
-        <v>4.293302936275722e-06</v>
+        <v>1.013368411406645e-08</v>
       </c>
       <c r="EH12" t="n">
-        <v>1.532964688522043e-06</v>
+        <v>2.459821502043269e-08</v>
       </c>
       <c r="EI12" t="n">
-        <v>2.734262807280174e-06</v>
+        <v>3.346750787613928e-08</v>
       </c>
       <c r="EJ12" t="n">
-        <v>3.329595074319514e-06</v>
+        <v>5.732651686685131e-08</v>
       </c>
       <c r="EK12" t="n">
-        <v>2.257075266243191e-06</v>
+        <v>4.526883046196417e-08</v>
       </c>
       <c r="EL12" t="n">
-        <v>2.980935278174002e-06</v>
+        <v>3.885094912448039e-08</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.528126517769124e-06</v>
+        <v>2.619801797720811e-08</v>
       </c>
       <c r="EN12" t="n">
-        <v>1.445613634132314e-06</v>
+        <v>3.271508619562269e-09</v>
       </c>
       <c r="EO12" t="n">
-        <v>1.6545982362004e-07</v>
+        <v>1.652304604249366e-08</v>
       </c>
       <c r="EP12" t="n">
-        <v>2.967679847643012e-06</v>
+        <v>4.799843722480546e-08</v>
       </c>
       <c r="EQ12" t="n">
-        <v>4.189843366475543e-06</v>
+        <v>4.818385690441573e-09</v>
       </c>
       <c r="ER12" t="n">
-        <v>6.451709850807674e-07</v>
+        <v>9.590893412791957e-09</v>
       </c>
       <c r="ES12" t="n">
-        <v>2.980047838718747e-06</v>
+        <v>4.678759069065563e-08</v>
       </c>
       <c r="ET12" t="n">
-        <v>2.621392809487588e-07</v>
+        <v>9.155487035172882e-09</v>
       </c>
       <c r="EU12" t="n">
-        <v>2.358168103455682e-06</v>
+        <v>3.491796185528528e-09</v>
       </c>
       <c r="EV12" t="n">
-        <v>8.250102837337181e-06</v>
+        <v>3.426010763973864e-08</v>
       </c>
       <c r="EW12" t="n">
-        <v>3.104035386058968e-06</v>
+        <v>2.926989850493555e-08</v>
       </c>
       <c r="EX12" t="n">
-        <v>5.333313310984522e-07</v>
+        <v>2.925379227747271e-08</v>
       </c>
       <c r="EY12" t="n">
-        <v>5.242859515419696e-06</v>
+        <v>1.192919114600954e-07</v>
       </c>
       <c r="EZ12" t="n">
-        <v>2.420688360871281e-06</v>
+        <v>6.385822981513911e-10</v>
       </c>
       <c r="FA12" t="n">
-        <v>2.779250053208671e-06</v>
+        <v>6.773668559389989e-08</v>
       </c>
       <c r="FB12" t="n">
-        <v>5.781857908004895e-07</v>
+        <v>2.11632276148066e-08</v>
       </c>
       <c r="FC12" t="n">
-        <v>2.496811248420272e-06</v>
+        <v>4.532979147597871e-08</v>
       </c>
       <c r="FD12" t="n">
-        <v>1.616124563952326e-06</v>
+        <v>5.394012347892385e-09</v>
       </c>
       <c r="FE12" t="n">
-        <v>6.888096777402097e-07</v>
+        <v>2.183497116448052e-08</v>
       </c>
       <c r="FF12" t="n">
-        <v>3.203573214705102e-06</v>
+        <v>4.430977806890724e-09</v>
       </c>
       <c r="FG12" t="n">
-        <v>2.7796368158306e-06</v>
+        <v>5.101449929156843e-08</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.220642957378004e-06</v>
+        <v>1.834570184655604e-08</v>
       </c>
       <c r="FI12" t="n">
-        <v>7.93597791926004e-06</v>
+        <v>4.366287598145391e-08</v>
       </c>
       <c r="FJ12" t="n">
-        <v>5.624848199659027e-06</v>
+        <v>3.202979570460229e-08</v>
       </c>
       <c r="FK12" t="n">
-        <v>1.392319518345175e-06</v>
+        <v>4.234456341123405e-09</v>
       </c>
       <c r="FL12" t="n">
-        <v>1.906897182379907e-06</v>
+        <v>6.907713157033868e-08</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.899686367323739e-06</v>
+        <v>3.479903476488744e-09</v>
       </c>
       <c r="FN12" t="n">
-        <v>4.980848189006792e-06</v>
+        <v>2.155802469872015e-08</v>
       </c>
       <c r="FO12" t="n">
-        <v>2.25697954192583e-06</v>
+        <v>1.107074041328815e-07</v>
       </c>
       <c r="FP12" t="n">
-        <v>9.302788726017752e-07</v>
+        <v>5.189738061517346e-08</v>
       </c>
       <c r="FQ12" t="n">
-        <v>1.936384251166601e-06</v>
+        <v>1.871704569111898e-09</v>
       </c>
       <c r="FR12" t="n">
-        <v>8.541070428691455e-08</v>
+        <v>1.211842004522623e-07</v>
       </c>
       <c r="FS12" t="n">
-        <v>4.317327011449379e-07</v>
+        <v>7.00549520615823e-08</v>
       </c>
       <c r="FT12" t="n">
-        <v>6.7933742684545e-06</v>
+        <v>7.589491701764928e-08</v>
       </c>
       <c r="FU12" t="n">
-        <v>1.106861759581079e-06</v>
+        <v>1.47385552651258e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>5.056060672359308e-06</v>
+        <v>1.10430946165252e-07</v>
       </c>
       <c r="FW12" t="n">
-        <v>3.324503495605313e-06</v>
+        <v>3.580230867328282e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>2.85154033008439e-06</v>
+        <v>7.970351134645171e-08</v>
       </c>
       <c r="FY12" t="n">
-        <v>7.508361250074813e-06</v>
+        <v>3.630488620842698e-08</v>
       </c>
       <c r="FZ12" t="n">
-        <v>3.665533085950301e-06</v>
+        <v>1.923443804230374e-08</v>
       </c>
       <c r="GA12" t="n">
-        <v>5.377922889238107e-07</v>
+        <v>8.740451562516682e-08</v>
       </c>
       <c r="GB12" t="n">
-        <v>1.012709390124655e-06</v>
+        <v>5.924536594648089e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>9.035566108650528e-06</v>
+        <v>1.331788297420644e-07</v>
       </c>
       <c r="GD12" t="n">
-        <v>4.976492618880002e-06</v>
+        <v>1.006206105103047e-07</v>
       </c>
       <c r="GE12" t="n">
-        <v>1.145580972661264e-05</v>
+        <v>1.349873173239757e-07</v>
       </c>
       <c r="GF12" t="n">
-        <v>2.375581971136853e-06</v>
+        <v>6.095303373143679e-09</v>
       </c>
       <c r="GG12" t="n">
-        <v>6.034134457877371e-06</v>
+        <v>1.980529518164076e-08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.582238473929465e-05</v>
+        <v>1.348798156497466e-11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002827119547873735</v>
+        <v>1.149182572018903e-11</v>
       </c>
       <c r="C13" t="n">
-        <v>8.192118548322469e-05</v>
+        <v>3.769944426079697e-12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0009904464241117239</v>
+        <v>3.655476095432153e-12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0005792116280645132</v>
+        <v>4.093997710286068e-12</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001295525697059929</v>
+        <v>2.26766804119205e-12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002463496057316661</v>
+        <v>1.129593467374956e-11</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0006039642030373216</v>
+        <v>2.384269864874611e-11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003396076499484479</v>
+        <v>1.808186239626863e-11</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002923593274317682</v>
+        <v>1.168948531721226e-11</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002749936189502478</v>
+        <v>3.783669558221625e-12</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001983816036954522</v>
+        <v>2.260021813790813e-12</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0007796060526743531</v>
+        <v>7.59800469068983e-12</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0001179338141810149</v>
+        <v>6.963107174184913e-12</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001180086866952479</v>
+        <v>9.945196575988913e-12</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001284280733671039</v>
+        <v>6.738097059477699e-12</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001117261563194916</v>
+        <v>2.463712740763402e-11</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0005274099530652165</v>
+        <v>8.635164631953796e-12</v>
       </c>
       <c r="S13" t="n">
-        <v>6.955540447961539e-05</v>
+        <v>1.199135062079915e-11</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002638575388118625</v>
+        <v>1.339001999556277e-11</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0001100517038139515</v>
+        <v>1.974252358816209e-12</v>
       </c>
       <c r="V13" t="n">
-        <v>5.509828042704612e-05</v>
+        <v>2.833971338850327e-12</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0001987869472941384</v>
+        <v>3.919829304893652e-12</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0001712125813355669</v>
+        <v>6.035455989150673e-12</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.471569213317707e-05</v>
+        <v>5.498158894313987e-13</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0004405521904118359</v>
+        <v>2.173016974693631e-12</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0002664168423507363</v>
+        <v>1.032830938829665e-11</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0002997800183948129</v>
+        <v>1.024803592680756e-11</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.551953265443444e-05</v>
+        <v>1.168831524622771e-12</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.273035013582557e-05</v>
+        <v>3.478825517586048e-12</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.965883661294356e-05</v>
+        <v>7.669136159460521e-12</v>
       </c>
       <c r="AF13" t="n">
-        <v>4.169160456513055e-05</v>
+        <v>7.466185655835567e-12</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.284749204292893e-05</v>
+        <v>1.107068343247919e-11</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.481911309994757e-05</v>
+        <v>9.962744604991025e-13</v>
       </c>
       <c r="AI13" t="n">
-        <v>8.14367740531452e-05</v>
+        <v>1.614987549074243e-12</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.712418977869675e-05</v>
+        <v>7.971413459872956e-12</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0002408875589026138</v>
+        <v>9.43531364150374e-12</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0004126321291550994</v>
+        <v>7.381518139781829e-12</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.000101866629847791</v>
+        <v>7.498356102697556e-12</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0001312788372160867</v>
+        <v>4.104723505538033e-12</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001029558334266767</v>
+        <v>6.892648778122901e-12</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0001581282849656418</v>
+        <v>6.147591116723028e-13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0002054010983556509</v>
+        <v>2.633347099406658e-13</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.501390215707943e-06</v>
+        <v>7.086953853624456e-12</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0001991538447327912</v>
+        <v>6.765791052409931e-12</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.000368370529031381</v>
+        <v>2.187193568620183e-12</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.001812325906939805</v>
+        <v>2.160734481962412e-12</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0002503782161511481</v>
+        <v>7.065141006956654e-12</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0001365241478197277</v>
+        <v>2.535167388517667e-12</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.525887925410643e-05</v>
+        <v>5.859715924289022e-12</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0006111047696322203</v>
+        <v>1.323910685940843e-11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.000611907453276217</v>
+        <v>9.738229320155334e-12</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.371092215180397e-05</v>
+        <v>3.368016802951512e-12</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0004599579842761159</v>
+        <v>4.516037717394727e-12</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.138042277190834e-05</v>
+        <v>2.908851978733473e-11</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0007439521141350269</v>
+        <v>2.061429325850295e-11</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0003510108508635312</v>
+        <v>9.470303014014192e-12</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.296054612495936e-05</v>
+        <v>2.91302702445928e-12</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0006309806485660374</v>
+        <v>2.116244506022991e-11</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0006277651409618556</v>
+        <v>1.514428231257081e-12</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001371631224174052</v>
+        <v>3.772846184774137e-12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.000207107252208516</v>
+        <v>2.335031300260137e-11</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0005062109557911754</v>
+        <v>2.804820785351492e-11</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001231174828717485</v>
+        <v>2.399704567002114e-12</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0004778506117872894</v>
+        <v>7.106742277995792e-12</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0001144817942986265</v>
+        <v>5.350110545560005e-12</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.000185232114745304</v>
+        <v>1.531723706205135e-11</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.430322926258668e-05</v>
+        <v>8.550169036322663e-13</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.700673889601603e-05</v>
+        <v>1.630154128004491e-12</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0004498281923588365</v>
+        <v>7.255394635780066e-12</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.608893116004765e-05</v>
+        <v>4.764666959589103e-12</v>
       </c>
       <c r="BT13" t="n">
-        <v>2.435520582366735e-05</v>
+        <v>1.165896979654635e-11</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.214436482172459e-05</v>
+        <v>1.643132505058098e-11</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.00097592209931463</v>
+        <v>1.145383961287383e-11</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.00012350564065855</v>
+        <v>4.196154708424604e-12</v>
       </c>
       <c r="BX13" t="n">
-        <v>6.602267967537045e-05</v>
+        <v>6.6113705222276e-13</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.748389230575413e-05</v>
+        <v>2.135520059398655e-12</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0002771430590655655</v>
+        <v>3.259194780377839e-12</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.252992458641529e-05</v>
+        <v>3.126639355408023e-12</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.568952110479586e-05</v>
+        <v>8.702259832876758e-13</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0003186925896443427</v>
+        <v>2.030565819655106e-12</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.724474249291234e-05</v>
+        <v>8.865684878942015e-13</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.000438880582805723</v>
+        <v>2.877382848046756e-13</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001201360864797607</v>
+        <v>6.476491977262799e-13</v>
       </c>
       <c r="CG13" t="n">
-        <v>6.488720828201622e-05</v>
+        <v>2.238601881990321e-12</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0001313787943217903</v>
+        <v>2.210629465940195e-12</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.000101289180747699</v>
+        <v>4.831106218197712e-13</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002050547482213005</v>
+        <v>1.103041269434613e-12</v>
       </c>
       <c r="CK13" t="n">
-        <v>3.20811195706483e-05</v>
+        <v>7.08274367974826e-13</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0001482470543123782</v>
+        <v>2.758108845479779e-12</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.000629699497949332</v>
+        <v>2.417739185939238e-12</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0002846221614163369</v>
+        <v>4.699104386857167e-12</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0001277362025575712</v>
+        <v>6.440168277138669e-12</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001115227700211108</v>
+        <v>7.77016211789272e-12</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0002872190088964999</v>
+        <v>2.490648486064284e-11</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0003387458273209631</v>
+        <v>1.091433714239809e-11</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0005325961392372847</v>
+        <v>1.176181634726658e-11</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0005274423165246844</v>
+        <v>1.747194077784953e-12</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001156456637545489</v>
+        <v>1.333713348095067e-11</v>
       </c>
       <c r="CV13" t="n">
-        <v>6.485571793746203e-05</v>
+        <v>3.148593798879551e-12</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0003759248938877136</v>
+        <v>1.359496825011075e-13</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.000121126497106161</v>
+        <v>1.922552178221237e-12</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0002167131315218285</v>
+        <v>2.706493449494696e-12</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.00015410287596751</v>
+        <v>4.82508998034259e-14</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.876785972854123e-05</v>
+        <v>1.371259442800588e-12</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001780912280082703</v>
+        <v>8.42100152630143e-13</v>
       </c>
       <c r="DC13" t="n">
-        <v>7.929607090773061e-05</v>
+        <v>1.33794695158021e-13</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0001209688998642378</v>
+        <v>1.682059005969627e-12</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001570016465848312</v>
+        <v>8.991526273538497e-12</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0003830165951512754</v>
+        <v>1.511943001353266e-11</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.700208278838545e-05</v>
+        <v>1.892361961575162e-11</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004212261119391769</v>
+        <v>4.91334403718291e-12</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0007710483041591942</v>
+        <v>1.04283248703041e-12</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001049451762810349</v>
+        <v>9.208895798695771e-12</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0002825668489094824</v>
+        <v>4.834359475236472e-12</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.000321944011375308</v>
+        <v>7.724404449405142e-12</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0007410061662085354</v>
+        <v>7.495327275508501e-12</v>
       </c>
       <c r="DN13" t="n">
-        <v>6.010737706674263e-05</v>
+        <v>9.139242314326612e-12</v>
       </c>
       <c r="DO13" t="n">
-        <v>7.237838144646958e-05</v>
+        <v>6.586514753742501e-12</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0003806388704106212</v>
+        <v>1.997215760829452e-12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0001410758995916694</v>
+        <v>1.574446085658709e-12</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0001777376455720514</v>
+        <v>3.458737636574671e-12</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002667712979018688</v>
+        <v>8.372963780645115e-12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0005640240269713104</v>
+        <v>2.9075899674047e-12</v>
       </c>
       <c r="DU13" t="n">
-        <v>1.772062569216359e-05</v>
+        <v>8.267628769098589e-12</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0002727547253016382</v>
+        <v>4.836253793272238e-12</v>
       </c>
       <c r="DW13" t="n">
-        <v>5.588740896200761e-05</v>
+        <v>5.202989948605019e-12</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0003828680492006242</v>
+        <v>1.651344425784851e-12</v>
       </c>
       <c r="DY13" t="n">
-        <v>3.304134588688612e-05</v>
+        <v>6.342372807499608e-12</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0005376178887672722</v>
+        <v>6.713283574877327e-12</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0002890453906729817</v>
+        <v>4.429353585300166e-12</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0001313621178269386</v>
+        <v>3.987432346114206e-12</v>
       </c>
       <c r="EC13" t="n">
-        <v>8.527722820872441e-05</v>
+        <v>1.086114705117769e-11</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002440399548504502</v>
+        <v>9.020879529475501e-12</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0004523632233031094</v>
+        <v>1.277777883501585e-11</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.000129553081933409</v>
+        <v>3.363335651651589e-12</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0005317702307365835</v>
+        <v>1.937698265730425e-12</v>
       </c>
       <c r="EH13" t="n">
-        <v>8.679715392645448e-06</v>
+        <v>1.542898838205464e-13</v>
       </c>
       <c r="EI13" t="n">
-        <v>7.384152559097856e-05</v>
+        <v>1.686335804069322e-13</v>
       </c>
       <c r="EJ13" t="n">
-        <v>6.461503653554246e-05</v>
+        <v>1.962705171998369e-12</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0003570728295017034</v>
+        <v>7.935149065607661e-12</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0003044160839635879</v>
+        <v>6.667843794466721e-12</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001702007430139929</v>
+        <v>3.527836117851735e-13</v>
       </c>
       <c r="EN13" t="n">
-        <v>8.613291720394045e-05</v>
+        <v>4.530815393005705e-12</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0001883113000076264</v>
+        <v>1.771299686786909e-12</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0001873466826509684</v>
+        <v>1.437780829723762e-13</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0001389974495396018</v>
+        <v>5.276890036043369e-12</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0003163699875585735</v>
+        <v>3.756810400962207e-13</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0003540256875567138</v>
+        <v>1.683908871716322e-12</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0001871980493888259</v>
+        <v>6.509826098316518e-12</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0005656842258758843</v>
+        <v>3.826994277034146e-12</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0004383919294923544</v>
+        <v>8.438625666296051e-12</v>
       </c>
       <c r="EW13" t="n">
-        <v>3.409129931242205e-05</v>
+        <v>4.418885396484384e-12</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001085550975403748</v>
+        <v>2.330438793329836e-12</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0003997321182396263</v>
+        <v>1.2018042810924e-12</v>
       </c>
       <c r="EZ13" t="n">
-        <v>7.111358718248084e-05</v>
+        <v>2.440114083013256e-12</v>
       </c>
       <c r="FA13" t="n">
-        <v>2.082779610645957e-05</v>
+        <v>3.879185167532384e-12</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001089287470676936</v>
+        <v>1.412304192864589e-12</v>
       </c>
       <c r="FC13" t="n">
-        <v>8.256832370534539e-05</v>
+        <v>2.271655628362235e-13</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0003413368249312043</v>
+        <v>1.957947692865503e-13</v>
       </c>
       <c r="FE13" t="n">
-        <v>5.538760160561651e-05</v>
+        <v>2.434506372536727e-12</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0002412108733551577</v>
+        <v>8.434902082354867e-13</v>
       </c>
       <c r="FG13" t="n">
-        <v>8.147388143697754e-05</v>
+        <v>1.887778995623979e-12</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0002292281424161047</v>
+        <v>2.072747355696958e-12</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.000172038096934557</v>
+        <v>4.892743328543947e-12</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0004990309826098382</v>
+        <v>4.922382380173618e-12</v>
       </c>
       <c r="FK13" t="n">
-        <v>7.823064515832812e-05</v>
+        <v>2.60826429898664e-12</v>
       </c>
       <c r="FL13" t="n">
-        <v>2.32631809922168e-05</v>
+        <v>1.458122685094043e-11</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0003577665193006396</v>
+        <v>4.178052868952786e-12</v>
       </c>
       <c r="FN13" t="n">
-        <v>5.025976861361414e-07</v>
+        <v>3.469849624640475e-12</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0002953442744910717</v>
+        <v>1.646981682978943e-11</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0003816848038695753</v>
+        <v>2.189368998595231e-11</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0003805953310802579</v>
+        <v>1.125577929472765e-12</v>
       </c>
       <c r="FR13" t="n">
-        <v>8.44670066726394e-05</v>
+        <v>9.314593367448776e-13</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0004253805382177234</v>
+        <v>1.357064807749886e-11</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0001868529507191852</v>
+        <v>2.724062642123215e-11</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0004244857700541615</v>
+        <v>3.798361365020542e-13</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0004435082664713264</v>
+        <v>5.727661400722894e-12</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0001880212221294641</v>
+        <v>1.77031358322699e-11</v>
       </c>
       <c r="FX13" t="n">
-        <v>1.827381856855936e-05</v>
+        <v>9.680235779629953e-12</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0005670806858688593</v>
+        <v>7.503633998873216e-12</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.000109992251964286</v>
+        <v>9.684952492761134e-12</v>
       </c>
       <c r="GA13" t="n">
-        <v>7.187593291746452e-05</v>
+        <v>1.594079729327902e-11</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001272879890166223</v>
+        <v>6.186231214788673e-12</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0001456372847314924</v>
+        <v>2.828392034470717e-12</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0003074747801292688</v>
+        <v>3.029181940006342e-12</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0002708270330913365</v>
+        <v>6.237813217346844e-12</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.000146746591781266</v>
+        <v>9.120754498881389e-12</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001335464476142079</v>
+        <v>1.153193426167709e-12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2.290873453603126e-06</v>
+        <v>1.188912346350435e-08</v>
       </c>
       <c r="B14" t="n">
-        <v>1.219993555423571e-05</v>
+        <v>2.134197174541441e-08</v>
       </c>
       <c r="C14" t="n">
-        <v>1.653571644055774e-06</v>
+        <v>1.225668899706989e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>8.426262866123579e-06</v>
+        <v>9.603995820839373e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>4.040339717903407e-06</v>
+        <v>1.085360423758175e-08</v>
       </c>
       <c r="F14" t="n">
-        <v>2.881834006984718e-06</v>
+        <v>1.163504848022967e-08</v>
       </c>
       <c r="G14" t="n">
-        <v>3.534508721259044e-07</v>
+        <v>9.829021152540918e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>3.363237794928864e-07</v>
+        <v>8.827008457501506e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>5.26138990153413e-07</v>
+        <v>1.296897478297865e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>3.145571326967911e-06</v>
+        <v>6.927471929429885e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>9.338449672213756e-06</v>
+        <v>2.349252525846168e-08</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41241071105469e-06</v>
+        <v>2.437679391675829e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>6.633220891671954e-06</v>
+        <v>2.220726713630938e-08</v>
       </c>
       <c r="N14" t="n">
-        <v>4.790950242750114e-06</v>
+        <v>2.167331203395406e-08</v>
       </c>
       <c r="O14" t="n">
-        <v>5.933532975177513e-06</v>
+        <v>1.52403956121816e-08</v>
       </c>
       <c r="P14" t="n">
-        <v>1.464732122258283e-06</v>
+        <v>7.354488573696472e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.958004986590822e-06</v>
+        <v>2.124265208180987e-10</v>
       </c>
       <c r="R14" t="n">
-        <v>6.133431043053861e-07</v>
+        <v>6.332785407181518e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>2.290329916831979e-07</v>
+        <v>6.191658297183267e-12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.307366230525076e-06</v>
+        <v>2.049059588671298e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>4.507634230321855e-07</v>
+        <v>4.931938857311025e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>1.186532131214335e-06</v>
+        <v>1.029938578867018e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41729572078475e-06</v>
+        <v>1.268987359637208e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.588841087141191e-06</v>
+        <v>4.416395693596087e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.062242401734693e-06</v>
+        <v>1.894867818208468e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.212564825436857e-06</v>
+        <v>1.491508583306711e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.951738340721931e-06</v>
+        <v>1.397987503537479e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.082591875790968e-07</v>
+        <v>5.311177275757473e-09</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.040085635395371e-06</v>
+        <v>7.293763815141574e-09</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.997767059147009e-07</v>
+        <v>3.205419041307778e-09</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.043180418491829e-06</v>
+        <v>4.996304259208273e-09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.242570760950912e-06</v>
+        <v>1.104827607179004e-08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.228050194868047e-07</v>
+        <v>1.874990296357737e-08</v>
       </c>
       <c r="AH14" t="n">
-        <v>9.043121167451318e-07</v>
+        <v>2.472756888138861e-09</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.167787667734956e-07</v>
+        <v>1.763548773681123e-08</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.409392496043438e-07</v>
+        <v>2.550096245279576e-10</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.528185180177388e-06</v>
+        <v>5.651167089837372e-09</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.174585918306548e-06</v>
+        <v>5.924539525636874e-09</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.309489665705769e-07</v>
+        <v>6.162966137424064e-09</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.392867024056613e-07</v>
+        <v>1.1376231068283e-09</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.067662765308341e-06</v>
+        <v>9.605116702005034e-09</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.331882029693588e-07</v>
+        <v>3.502936607446827e-09</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.163915137833101e-07</v>
+        <v>1.588995601764509e-09</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.773218620357511e-07</v>
+        <v>3.936350356781304e-09</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.827251687966054e-07</v>
+        <v>5.476699094231208e-10</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.846014457551064e-07</v>
+        <v>3.200988807350313e-09</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.193687790480908e-06</v>
+        <v>2.041870672542245e-08</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.307191935979063e-07</v>
+        <v>9.39857081050377e-09</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.672656364666182e-06</v>
+        <v>3.200789633339696e-09</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.09168274775584e-06</v>
+        <v>2.44438851382256e-08</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.079164111521095e-07</v>
+        <v>1.890767364898238e-08</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.114114525080367e-07</v>
+        <v>3.607355747448082e-09</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.640527443669271e-06</v>
+        <v>1.804049576392686e-09</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.071959673026868e-06</v>
+        <v>5.438704153704066e-09</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.203457145493303e-06</v>
+        <v>1.530342852440469e-09</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.097669837690773e-06</v>
+        <v>7.914002786435503e-09</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.71483338312828e-06</v>
+        <v>2.267409371370377e-09</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.77147433078062e-06</v>
+        <v>1.069782840090738e-08</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.070353497809265e-06</v>
+        <v>1.40246267932298e-08</v>
       </c>
       <c r="BH14" t="n">
-        <v>1.650490162319329e-06</v>
+        <v>4.114157903245541e-09</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.241892164216551e-06</v>
+        <v>1.917674685714132e-09</v>
       </c>
       <c r="BJ14" t="n">
-        <v>2.413376932963729e-06</v>
+        <v>1.196008359016787e-08</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.199807684315601e-07</v>
+        <v>5.490144339148628e-09</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.934009560500272e-06</v>
+        <v>3.1866331795527e-09</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.326801677554613e-06</v>
+        <v>1.144511330153364e-08</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.421634920006909e-06</v>
+        <v>2.477775762343981e-10</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.146328600043489e-06</v>
+        <v>5.261479696372362e-09</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.445811221856275e-06</v>
+        <v>1.075010658269093e-08</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.066563168540597e-07</v>
+        <v>4.383255980400236e-10</v>
       </c>
       <c r="BR14" t="n">
-        <v>2.573276276507386e-07</v>
+        <v>8.866255285511215e-09</v>
       </c>
       <c r="BS14" t="n">
-        <v>5.065421646577306e-07</v>
+        <v>6.840483735004455e-09</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.877170903862861e-07</v>
+        <v>5.774544398207127e-09</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.161378228673129e-07</v>
+        <v>6.194416646287948e-10</v>
       </c>
       <c r="BV14" t="n">
-        <v>3.835860752587905e-06</v>
+        <v>1.052155340630634e-08</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.850643002399011e-06</v>
+        <v>4.064657943558814e-09</v>
       </c>
       <c r="BX14" t="n">
-        <v>1.255072902495158e-06</v>
+        <v>3.396461556448571e-09</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.899149530501745e-07</v>
+        <v>5.605729214153143e-09</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.345264758536359e-07</v>
+        <v>1.127437876391468e-08</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.909671027533477e-06</v>
+        <v>6.241295036346628e-09</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.805267058647587e-07</v>
+        <v>2.717770897220362e-09</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.436198868366773e-07</v>
+        <v>1.779434377624511e-09</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.212795280343016e-08</v>
+        <v>2.244984864674393e-09</v>
       </c>
       <c r="CE14" t="n">
-        <v>2.059753342109616e-06</v>
+        <v>6.590562762198715e-09</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.210920004268701e-06</v>
+        <v>3.284128524683183e-11</v>
       </c>
       <c r="CG14" t="n">
-        <v>7.219206850095361e-07</v>
+        <v>4.302272316181188e-09</v>
       </c>
       <c r="CH14" t="n">
-        <v>3.921468589851429e-07</v>
+        <v>4.990936997018025e-09</v>
       </c>
       <c r="CI14" t="n">
-        <v>9.986808890971588e-07</v>
+        <v>4.061640801467092e-09</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.022385103828128e-08</v>
+        <v>5.71525160530939e-10</v>
       </c>
       <c r="CK14" t="n">
-        <v>3.269042849751713e-07</v>
+        <v>9.872804795918455e-10</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.137775711868017e-06</v>
+        <v>2.411722821449303e-09</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.106150077452185e-06</v>
+        <v>1.033880714373936e-08</v>
       </c>
       <c r="CN14" t="n">
-        <v>6.820673092988727e-08</v>
+        <v>1.452363207476992e-08</v>
       </c>
       <c r="CO14" t="n">
-        <v>7.878612109379901e-07</v>
+        <v>1.42630582899983e-08</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.718480573093984e-06</v>
+        <v>1.153585582613914e-08</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.61562934408721e-06</v>
+        <v>4.764007854873853e-09</v>
       </c>
       <c r="CR14" t="n">
-        <v>6.842395094963649e-08</v>
+        <v>9.15688680436233e-09</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.081824959532241e-06</v>
+        <v>7.443508920346176e-09</v>
       </c>
       <c r="CT14" t="n">
-        <v>7.481263537556515e-07</v>
+        <v>5.365799360390611e-09</v>
       </c>
       <c r="CU14" t="n">
-        <v>5.532658633455867e-07</v>
+        <v>2.041280700026959e-09</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.358077241775391e-07</v>
+        <v>5.730369512235711e-10</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.87603814083559e-06</v>
+        <v>5.473902220387572e-09</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.05510150660848e-06</v>
+        <v>3.790668057224167e-10</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.447125555387174e-06</v>
+        <v>6.541110764146651e-09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>6.944324013602454e-07</v>
+        <v>4.789271645933013e-09</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.242087932951108e-06</v>
+        <v>5.207448694477534e-09</v>
       </c>
       <c r="DB14" t="n">
-        <v>3.282627005773975e-07</v>
+        <v>6.886446968223936e-10</v>
       </c>
       <c r="DC14" t="n">
-        <v>4.388445233871607e-07</v>
+        <v>1.844430386199747e-09</v>
       </c>
       <c r="DD14" t="n">
-        <v>8.129781576826645e-07</v>
+        <v>2.282524391716834e-09</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.679919819252973e-06</v>
+        <v>6.581589162557577e-10</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.554784887503047e-07</v>
+        <v>4.262521891007509e-09</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.221708311684779e-06</v>
+        <v>7.225824383283452e-10</v>
       </c>
       <c r="DH14" t="n">
-        <v>4.209968210489023e-06</v>
+        <v>4.94054175348424e-09</v>
       </c>
       <c r="DI14" t="n">
-        <v>7.207138423837023e-07</v>
+        <v>1.173656949404744e-09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.386997382724076e-06</v>
+        <v>7.681244085233629e-09</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.820122967430507e-07</v>
+        <v>7.683069735975323e-10</v>
       </c>
       <c r="DL14" t="n">
-        <v>1.818767827899137e-06</v>
+        <v>1.196544197057392e-08</v>
       </c>
       <c r="DM14" t="n">
-        <v>1.134023932536365e-06</v>
+        <v>9.470407569267536e-09</v>
       </c>
       <c r="DN14" t="n">
-        <v>5.445298256745446e-07</v>
+        <v>6.28984753170414e-10</v>
       </c>
       <c r="DO14" t="n">
-        <v>9.044593411999813e-07</v>
+        <v>1.632803448003983e-09</v>
       </c>
       <c r="DP14" t="n">
-        <v>1.185248947876971e-06</v>
+        <v>2.545339938819779e-09</v>
       </c>
       <c r="DQ14" t="n">
-        <v>6.621878583246144e-07</v>
+        <v>2.468310222880632e-09</v>
       </c>
       <c r="DR14" t="n">
-        <v>1.436942227428517e-07</v>
+        <v>5.205989417333967e-09</v>
       </c>
       <c r="DS14" t="n">
-        <v>5.003542469239619e-07</v>
+        <v>7.055021011836971e-10</v>
       </c>
       <c r="DT14" t="n">
-        <v>4.109670044272207e-07</v>
+        <v>6.047926603969245e-10</v>
       </c>
       <c r="DU14" t="n">
-        <v>2.234079801155531e-07</v>
+        <v>9.862480609967861e-09</v>
       </c>
       <c r="DV14" t="n">
-        <v>1.875892053249117e-06</v>
+        <v>4.730945413200516e-09</v>
       </c>
       <c r="DW14" t="n">
-        <v>6.332592192848097e-07</v>
+        <v>2.675903498783327e-09</v>
       </c>
       <c r="DX14" t="n">
-        <v>1.672741177571879e-06</v>
+        <v>2.26572940964509e-10</v>
       </c>
       <c r="DY14" t="n">
-        <v>2.567724777691183e-06</v>
+        <v>4.476563564281832e-09</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.449946082260794e-08</v>
+        <v>3.689070382506543e-09</v>
       </c>
       <c r="EA14" t="n">
-        <v>5.869749770681665e-07</v>
+        <v>1.74625947035878e-09</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.082500941469334e-06</v>
+        <v>1.143867667252607e-09</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.170280938822543e-07</v>
+        <v>3.37262107130698e-09</v>
       </c>
       <c r="ED14" t="n">
-        <v>4.048739299378212e-07</v>
+        <v>1.143401551217949e-08</v>
       </c>
       <c r="EE14" t="n">
-        <v>4.17150602061156e-07</v>
+        <v>4.493519334403118e-09</v>
       </c>
       <c r="EF14" t="n">
-        <v>6.59839827221731e-07</v>
+        <v>9.244769394456398e-10</v>
       </c>
       <c r="EG14" t="n">
-        <v>1.462312525291054e-06</v>
+        <v>2.628160578055372e-09</v>
       </c>
       <c r="EH14" t="n">
-        <v>4.414318368617387e-07</v>
+        <v>2.499498830133007e-09</v>
       </c>
       <c r="EI14" t="n">
-        <v>1.044515556714032e-06</v>
+        <v>4.954050059069459e-09</v>
       </c>
       <c r="EJ14" t="n">
-        <v>4.874485171058041e-07</v>
+        <v>3.002513793148864e-09</v>
       </c>
       <c r="EK14" t="n">
-        <v>9.187646128339111e-07</v>
+        <v>4.634983508111645e-09</v>
       </c>
       <c r="EL14" t="n">
-        <v>4.001599336334039e-07</v>
+        <v>1.509012248490649e-09</v>
       </c>
       <c r="EM14" t="n">
-        <v>4.281771168734849e-07</v>
+        <v>5.103426015118373e-10</v>
       </c>
       <c r="EN14" t="n">
-        <v>4.838335030399321e-07</v>
+        <v>3.116684688109217e-09</v>
       </c>
       <c r="EO14" t="n">
-        <v>2.92838279847274e-07</v>
+        <v>1.948498029591406e-09</v>
       </c>
       <c r="EP14" t="n">
-        <v>6.381978323588555e-07</v>
+        <v>4.500734451795552e-09</v>
       </c>
       <c r="EQ14" t="n">
-        <v>1.487221993556886e-06</v>
+        <v>3.655842295557932e-10</v>
       </c>
       <c r="ER14" t="n">
-        <v>1.580351067786978e-07</v>
+        <v>2.078107019798381e-09</v>
       </c>
       <c r="ES14" t="n">
-        <v>1.260455860574439e-06</v>
+        <v>2.694726664032032e-09</v>
       </c>
       <c r="ET14" t="n">
-        <v>3.194431741349035e-08</v>
+        <v>3.482447663571975e-10</v>
       </c>
       <c r="EU14" t="n">
-        <v>5.262411377771059e-07</v>
+        <v>2.038589741459873e-09</v>
       </c>
       <c r="EV14" t="n">
-        <v>2.650047690622159e-06</v>
+        <v>7.402317092619626e-10</v>
       </c>
       <c r="EW14" t="n">
-        <v>7.388026688204263e-07</v>
+        <v>4.741104842054256e-09</v>
       </c>
       <c r="EX14" t="n">
-        <v>2.066172299919344e-07</v>
+        <v>1.877731525823378e-09</v>
       </c>
       <c r="EY14" t="n">
-        <v>1.751650756887102e-06</v>
+        <v>8.139272367202466e-09</v>
       </c>
       <c r="EZ14" t="n">
-        <v>8.479165103381092e-07</v>
+        <v>7.924016304228232e-11</v>
       </c>
       <c r="FA14" t="n">
-        <v>8.368402291125676e-07</v>
+        <v>6.045554279410226e-09</v>
       </c>
       <c r="FB14" t="n">
-        <v>2.174817410605101e-07</v>
+        <v>2.375444063673626e-09</v>
       </c>
       <c r="FC14" t="n">
-        <v>1.094480921892682e-06</v>
+        <v>4.303315481735126e-09</v>
       </c>
       <c r="FD14" t="n">
-        <v>2.689046993964439e-07</v>
+        <v>7.062395668278043e-10</v>
       </c>
       <c r="FE14" t="n">
-        <v>2.291637883899966e-07</v>
+        <v>1.246004188715233e-09</v>
       </c>
       <c r="FF14" t="n">
-        <v>1.240493020304712e-06</v>
+        <v>4.02878730376699e-10</v>
       </c>
       <c r="FG14" t="n">
-        <v>1.192246031678224e-06</v>
+        <v>4.980097223494795e-09</v>
       </c>
       <c r="FH14" t="n">
-        <v>2.370981349031354e-07</v>
+        <v>7.476405272655029e-09</v>
       </c>
       <c r="FI14" t="n">
-        <v>2.56267276199651e-06</v>
+        <v>4.720305923910928e-09</v>
       </c>
       <c r="FJ14" t="n">
-        <v>1.475184149057895e-06</v>
+        <v>3.609952337058075e-09</v>
       </c>
       <c r="FK14" t="n">
-        <v>2.246451913379133e-07</v>
+        <v>1.009988181976951e-08</v>
       </c>
       <c r="FL14" t="n">
-        <v>1.127171799453208e-06</v>
+        <v>8.334561485412451e-09</v>
       </c>
       <c r="FM14" t="n">
-        <v>3.293700672202249e-07</v>
+        <v>1.278470884713556e-09</v>
       </c>
       <c r="FN14" t="n">
-        <v>1.964310740731889e-06</v>
+        <v>6.204744273929919e-09</v>
       </c>
       <c r="FO14" t="n">
-        <v>1.060306203726213e-06</v>
+        <v>1.701736174197777e-08</v>
       </c>
       <c r="FP14" t="n">
-        <v>2.092707234169211e-07</v>
+        <v>7.505063237545073e-10</v>
       </c>
       <c r="FQ14" t="n">
-        <v>6.683203537249938e-07</v>
+        <v>6.685272779805018e-09</v>
       </c>
       <c r="FR14" t="n">
-        <v>5.127467943566444e-07</v>
+        <v>1.329367016467131e-08</v>
       </c>
       <c r="FS14" t="n">
-        <v>8.495585461787414e-07</v>
+        <v>4.331969005733072e-09</v>
       </c>
       <c r="FT14" t="n">
-        <v>2.483011257936596e-06</v>
+        <v>1.265029325736577e-08</v>
       </c>
       <c r="FU14" t="n">
-        <v>1.954760335820538e-07</v>
+        <v>1.509409708333465e-09</v>
       </c>
       <c r="FV14" t="n">
-        <v>1.122543949350074e-06</v>
+        <v>1.028891905008322e-08</v>
       </c>
       <c r="FW14" t="n">
-        <v>3.060106337215984e-07</v>
+        <v>1.653790704381208e-08</v>
       </c>
       <c r="FX14" t="n">
-        <v>1.060319277712551e-06</v>
+        <v>6.859790513402686e-09</v>
       </c>
       <c r="FY14" t="n">
-        <v>2.972446509375004e-06</v>
+        <v>3.335062892517726e-09</v>
       </c>
       <c r="FZ14" t="n">
-        <v>1.179495711767231e-06</v>
+        <v>3.491060773797017e-09</v>
       </c>
       <c r="GA14" t="n">
-        <v>1.474696347258941e-07</v>
+        <v>8.39317770839898e-09</v>
       </c>
       <c r="GB14" t="n">
-        <v>1.425268010279979e-07</v>
+        <v>1.626269563459459e-09</v>
       </c>
       <c r="GC14" t="n">
-        <v>2.929896254499909e-06</v>
+        <v>1.009817385266842e-08</v>
       </c>
       <c r="GD14" t="n">
-        <v>1.359152975055622e-06</v>
+        <v>1.675865135553067e-08</v>
       </c>
       <c r="GE14" t="n">
-        <v>2.771699655568227e-06</v>
+        <v>5.065791341962722e-09</v>
       </c>
       <c r="GF14" t="n">
-        <v>7.9379708495253e-07</v>
+        <v>2.692376988022716e-09</v>
       </c>
       <c r="GG14" t="n">
-        <v>1.898417053780577e-06</v>
+        <v>1.155661677465503e-09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.001245457213371992</v>
+        <v>0.003588480874896049</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01546184159815311</v>
+        <v>0.1754772663116455</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001463839435018599</v>
+        <v>0.08389782905578613</v>
       </c>
       <c r="D15" t="n">
-        <v>0.005295494571328163</v>
+        <v>0.0896642655134201</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002315460238605738</v>
+        <v>0.05093009397387505</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01001224853098392</v>
+        <v>0.2723254263401031</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001648077159188688</v>
+        <v>0.007148317061364651</v>
       </c>
       <c r="H15" t="n">
-        <v>0.005602437071502209</v>
+        <v>0.1110406816005707</v>
       </c>
       <c r="I15" t="n">
-        <v>0.002026045229285955</v>
+        <v>0.09657202661037445</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002246155869215727</v>
+        <v>0.04775628075003624</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01492876280099154</v>
+        <v>0.221184253692627</v>
       </c>
       <c r="L15" t="n">
-        <v>7.257933611981571e-05</v>
+        <v>0.09178270399570465</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003485613269731402</v>
+        <v>0.1856189221143723</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0003918497823178768</v>
+        <v>0.08649443089962006</v>
       </c>
       <c r="O15" t="n">
-        <v>0.009263935498893261</v>
+        <v>0.3504213094711304</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0003732723416760564</v>
+        <v>0.0308297835290432</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.001817542244680226</v>
+        <v>0.06304618716239929</v>
       </c>
       <c r="R15" t="n">
-        <v>0.002710676752030849</v>
+        <v>0.07507918030023575</v>
       </c>
       <c r="S15" t="n">
-        <v>9.309680899605155e-05</v>
+        <v>0.03287511318922043</v>
       </c>
       <c r="T15" t="n">
-        <v>0.001390732475556433</v>
+        <v>0.02579126693308353</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0002771778963506222</v>
+        <v>0.008890777826309204</v>
       </c>
       <c r="V15" t="n">
-        <v>0.001560074626468122</v>
+        <v>0.0292234942317009</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001769328489899635</v>
+        <v>0.04600946605205536</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0009887289488688111</v>
+        <v>0.08214346319437027</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0004971513990312815</v>
+        <v>0.05721984431147575</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.002398134674876928</v>
+        <v>0.04770302772521973</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.001473950571380556</v>
+        <v>0.01778214611113071</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0006549510871991515</v>
+        <v>0.005145914852619171</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.000676455965731293</v>
+        <v>0.00549045205116272</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0001575934438733384</v>
+        <v>0.009326262399554253</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0004231156199239194</v>
+        <v>0.05579106882214546</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001372957136482</v>
+        <v>0.09694057703018188</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.82639588881284e-05</v>
+        <v>0.1011683717370033</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.000102632911875844</v>
+        <v>0.002908015623688698</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0007661766139790416</v>
+        <v>0.1672690510749817</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0002431947214063257</v>
+        <v>0.003902435768395662</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.002220676513388753</v>
+        <v>0.03544165939092636</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.001214051153510809</v>
+        <v>0.01680378429591656</v>
       </c>
       <c r="AM15" t="n">
-        <v>8.496857481077313e-05</v>
+        <v>0.01861554197967052</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.001002766657620668</v>
+        <v>0.001276838476769626</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0006832382641732693</v>
+        <v>0.08374714851379395</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.00231857574544847</v>
+        <v>0.03440401330590248</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.001060003647580743</v>
+        <v>0.006371700204908848</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0009299839730374515</v>
+        <v>0.03885895758867264</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.001875805202871561</v>
+        <v>5.479995161294937e-05</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0009473378304392099</v>
+        <v>0.001006610691547394</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.008395375683903694</v>
+        <v>0.2367745637893677</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.001314165536314249</v>
+        <v>0.05681091919541359</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.001984516391530633</v>
+        <v>0.0171338003128767</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.001679024891927838</v>
+        <v>0.122321218252182</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.005527028348296881</v>
+        <v>0.2685075104236603</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.003476077690720558</v>
+        <v>0.006055990234017372</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.001898469752632082</v>
+        <v>0.04327588528394699</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.003044159384444356</v>
+        <v>0.01073230803012848</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0006030838703736663</v>
+        <v>0.03762028738856316</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.00386244198307395</v>
+        <v>0.01339488849043846</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.003991644363850355</v>
+        <v>0.07052470743656158</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0006384118460118771</v>
+        <v>0.08296036720275879</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0005273850401863456</v>
+        <v>0.07056888192892075</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.002036046469584107</v>
+        <v>0.0468631237745285</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0008908925228752196</v>
+        <v>0.02349699102342129</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.00159935827832669</v>
+        <v>0.1186394765973091</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.002371970564126968</v>
+        <v>0.04080623015761375</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0004160563694313169</v>
+        <v>0.004416675306856632</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.002615454373881221</v>
+        <v>0.1397288292646408</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.002045974368229508</v>
+        <v>0.03764829412102699</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0004096213961020112</v>
+        <v>0.04461141303181648</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.001256292802281678</v>
+        <v>0.08753516525030136</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0002159878786187619</v>
+        <v>0.04002336412668228</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.001781593076884747</v>
+        <v>0.03275115042924881</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.001467965426854789</v>
+        <v>0.05815190821886063</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.001073305960744619</v>
+        <v>0.0314842164516449</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.000140943651786074</v>
+        <v>0.014991938136518</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.005299355369061232</v>
+        <v>0.1106021553277969</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.001321199699304998</v>
+        <v>0.0001920610666275024</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0004016845487058163</v>
+        <v>0.02380545437335968</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0009776173392310739</v>
+        <v>0.01960070058703423</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.002358305267989635</v>
+        <v>0.1572341620922089</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0003105480864178389</v>
+        <v>0.07192549854516983</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.000399612239561975</v>
+        <v>0.02607092261314392</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.001136997598223388</v>
+        <v>0.02143793553113937</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0004814970889128745</v>
+        <v>0.01062487065792084</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.002834957558661699</v>
+        <v>0.04516884684562683</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.00122010987251997</v>
+        <v>0.02823625318706036</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0006404594168998301</v>
+        <v>0.02530990727245808</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.000487439101561904</v>
+        <v>0.04459897428750992</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.001005078665912151</v>
+        <v>0.07632357627153397</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.001201967243105173</v>
+        <v>0.01208960823714733</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.001061215065419674</v>
+        <v>0.008688874542713165</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.00118014111649245</v>
+        <v>0.00502315629273653</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.003844058373942971</v>
+        <v>0.03192910924553871</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.001524445717222989</v>
+        <v>0.05921252816915512</v>
       </c>
       <c r="CO15" t="n">
-        <v>9.160488843917847e-05</v>
+        <v>0.08560289442539215</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.004370732232928276</v>
+        <v>0.06016045808792114</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.001350517617538571</v>
+        <v>0.02260012924671173</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.004021800588816404</v>
+        <v>0.04325510188937187</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.003050947096198797</v>
+        <v>0.08075940608978271</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.002665614243596792</v>
+        <v>0.08976101875305176</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.00126585632096976</v>
+        <v>0.04084617272019386</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0004336816200520843</v>
+        <v>0.01070549245923758</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.002670650137588382</v>
+        <v>0.03635653853416443</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.001442714594304562</v>
+        <v>0.04057706147432327</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.001423942390829325</v>
+        <v>0.0420919694006443</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0004327999777160585</v>
+        <v>0.04357080534100533</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0008129006600938737</v>
+        <v>0.09658728539943695</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.001186193199828267</v>
+        <v>0.001004126155748963</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.001843318110331893</v>
+        <v>0.01365191861987114</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.00103049969766289</v>
+        <v>0.01598870009183884</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.001229381537996233</v>
+        <v>0.03174421936273575</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.002303440822288394</v>
+        <v>0.1381511688232422</v>
       </c>
       <c r="DG15" t="n">
-        <v>8.960634295362979e-05</v>
+        <v>0.01718944497406483</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.003000786760821939</v>
+        <v>0.03927958011627197</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.004141310695558786</v>
+        <v>0.0315578281879425</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.003536887234076858</v>
+        <v>0.04135892912745476</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.001465933280996978</v>
+        <v>0.03059115260839462</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.002585696056485176</v>
+        <v>0.07139803469181061</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.003962639719247818</v>
+        <v>0.03213439881801605</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.0004042307264171541</v>
+        <v>0.011628158390522</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.001753084943629801</v>
+        <v>0.01469168905168772</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.001249867142178118</v>
+        <v>0.01610390469431877</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.001008244347758591</v>
+        <v>0.05087985098361969</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.001522928476333618</v>
+        <v>0.001498735509812832</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.002652009017765522</v>
+        <v>0.02966863475739956</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.001891567604616284</v>
+        <v>0.04629745334386826</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.001622137962840497</v>
+        <v>0.08788726478815079</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.0004823528579436243</v>
+        <v>0.05421891435980797</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0003090009558945894</v>
+        <v>0.01310579851269722</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.00157054967712611</v>
+        <v>0.01815887354314327</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.001474916702136397</v>
+        <v>0.09110261499881744</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.001802443992346525</v>
+        <v>0.02097230963408947</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.001872900640591979</v>
+        <v>0.01211537979543209</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0007396513246931136</v>
+        <v>0.002096500713378191</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0004406601947266608</v>
+        <v>0.05897617340087891</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0008972763316705823</v>
+        <v>0.05584345757961273</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.003233414143323898</v>
+        <v>0.08306059986352921</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.001828268053941429</v>
+        <v>0.01141693443059921</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.003158614505082369</v>
+        <v>0.02039641141891479</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.001729679643176496</v>
+        <v>0.003248782828450203</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0002120610442943871</v>
+        <v>0.06480743736028671</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0003932635299861431</v>
+        <v>0.01195141300559044</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0009249058784916997</v>
+        <v>0.03585989773273468</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.001445175847038627</v>
+        <v>0.00791294127702713</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0002360805519856513</v>
+        <v>0.01958600245416164</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.000460100214695558</v>
+        <v>0.05353230983018875</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.0002460525138303638</v>
+        <v>0.0193315576761961</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.001211396069265902</v>
+        <v>0.05210734531283379</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.001052818377502263</v>
+        <v>0.02312120422720909</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.00163926905952394</v>
+        <v>0.03952920809388161</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.001951850485056639</v>
+        <v>0.01025277376174927</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.001112898578867316</v>
+        <v>0.08307567983865738</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.00336954602971673</v>
+        <v>0.02187694609165192</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.004063386470079422</v>
+        <v>0.0189945362508297</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.0003972573904320598</v>
+        <v>0.009789644740521908</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0006908638752065599</v>
+        <v>0.008006587624549866</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.00249137356877327</v>
+        <v>0.06047195196151733</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001136179314926267</v>
+        <v>0.02472326532006264</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0002982823643833399</v>
+        <v>0.04022229835391045</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0004168734303675592</v>
+        <v>0.03464622050523758</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.00070076750125736</v>
+        <v>0.08363703638315201</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.001895993947982788</v>
+        <v>0.02717901766300201</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.001635120483115315</v>
+        <v>0.005897324997931719</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.001466447836719453</v>
+        <v>0.02653677389025688</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.00059816415887326</v>
+        <v>0.01177870482206345</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0008614413673058152</v>
+        <v>0.03857159242033958</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.001897209323942661</v>
+        <v>0.05389727652072906</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.002421315293759108</v>
+        <v>0.01913815177977085</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.001208629109896719</v>
+        <v>0.0436582900583744</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.001148446113802493</v>
+        <v>0.09744389355182648</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.001344852615147829</v>
+        <v>0.001129563897848129</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.001098757027648389</v>
+        <v>0.04737155884504318</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.001001542434096336</v>
+        <v>0.1258883029222488</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.001901992713101208</v>
+        <v>0.02287298813462257</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.001303351134993136</v>
+        <v>0.007542748935520649</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.002674686722457409</v>
+        <v>0.02969642728567123</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.002031112322583795</v>
+        <v>0.05603181570768356</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.000311702664475888</v>
+        <v>0.1601847410202026</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.00214657187461853</v>
+        <v>0.06338514387607574</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0008319655316881835</v>
+        <v>0.01311007887125015</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0007241158746182919</v>
+        <v>0.1552995145320892</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.001149687450379133</v>
+        <v>0.04036172479391098</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.002676392439752817</v>
+        <v>0.02457334846258163</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.001728379284031689</v>
+        <v>0.05118872225284576</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.001157073653303087</v>
+        <v>0.1200119405984879</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0006299962988123298</v>
+        <v>0.02896755747497082</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.0006090408423915505</v>
+        <v>0.1142467856407166</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.001168292248621583</v>
+        <v>0.07756201922893524</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.002607307862490416</v>
+        <v>0.0781366229057312</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.000306862813886255</v>
+        <v>0.03216898441314697</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0008824312826618552</v>
+        <v>0.01863660290837288</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.815565130731557e-05</v>
+        <v>5.199653969611973e-07</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001565709942951798</v>
+        <v>0.0003189934941474348</v>
       </c>
       <c r="C16" t="n">
-        <v>1.26674203784205e-05</v>
+        <v>5.784914901596494e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000457170361187309</v>
+        <v>5.989768033032306e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0002701076446101069</v>
+        <v>0.0001916272012749687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008186211343854666</v>
+        <v>0.0004376482975203544</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001530087320134044</v>
+        <v>0.0001735647965688258</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002840648230630904</v>
+        <v>0.0002665536594577134</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001367890799883753</v>
+        <v>7.686294702580199e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001472130534239113</v>
+        <v>6.082434265408665e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00157888769172132</v>
+        <v>0.000393272377550602</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001077939014066942</v>
+        <v>0.0001786977081792429</v>
       </c>
       <c r="M16" t="n">
-        <v>0.000343574647558853</v>
+        <v>0.0001354722771793604</v>
       </c>
       <c r="N16" t="n">
-        <v>6.767595186829567e-05</v>
+        <v>0.0003832455258816481</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006443627644330263</v>
+        <v>0.0005694451392628253</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0001062222363543697</v>
+        <v>0.000108111540612299</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001366391807096079</v>
+        <v>0.0001315173867624253</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0002056571975117549</v>
+        <v>7.357462891377509e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>4.221783456159756e-05</v>
+        <v>1.517442797194235e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001331719686277211</v>
+        <v>1.355622225673869e-05</v>
       </c>
       <c r="U16" t="n">
-        <v>8.605309176346054e-08</v>
+        <v>7.035050657577813e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0001851942506618798</v>
+        <v>5.287229942041449e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001550614833831787</v>
+        <v>8.935031655710191e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>5.029028397984803e-05</v>
+        <v>7.141432433854789e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.054737731465138e-05</v>
+        <v>6.932628457434475e-05</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0002518523251637816</v>
+        <v>0.000128787592984736</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.000117480187327601</v>
+        <v>6.212036532815546e-05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0001337580324616283</v>
+        <v>9.151654376182705e-05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0001022394935716875</v>
+        <v>1.392881677020341e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.713298843242228e-06</v>
+        <v>3.609630584833212e-05</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.026272522925865e-05</v>
+        <v>0.0001521162921562791</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0001428302639396861</v>
+        <v>0.0001496195036452264</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0001016451788018458</v>
+        <v>0.0001324366312474012</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.739970270544291e-05</v>
+        <v>8.998340490506962e-06</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.45267504194635e-05</v>
+        <v>0.0002445131540298462</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5.365829565562308e-05</v>
+        <v>3.928699516109191e-05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0001755146950017661</v>
+        <v>3.164224835927598e-05</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0002128897467628121</v>
+        <v>2.488813333911821e-05</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0001380799221806228</v>
+        <v>1.661005080677569e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.494254997349344e-05</v>
+        <v>2.997784758917987e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0001060866707121022</v>
+        <v>7.930064020911232e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001001038472168148</v>
+        <v>5.28917480551172e-05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.626632992061786e-05</v>
+        <v>3.95319948438555e-05</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.728830779436976e-05</v>
+        <v>0.0001270330540137365</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.289576802169904e-05</v>
+        <v>2.765664430626202e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.486376075074077e-05</v>
+        <v>3.131171979475766e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.001028591301292181</v>
+        <v>0.0003932829713448882</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0002186918281950057</v>
+        <v>3.989207471022382e-05</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.0001060617360053584</v>
+        <v>6.340322579490021e-05</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0001803828781703487</v>
+        <v>0.0002076934179058298</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0004221648559905589</v>
+        <v>0.0003355749067850411</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0002505310112610459</v>
+        <v>3.141295746900141e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.567755629774183e-05</v>
+        <v>9.327141742687672e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0001312583190156147</v>
+        <v>1.574527050252073e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0001128134463215247</v>
+        <v>1.480257924413309e-05</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.000443947094026953</v>
+        <v>6.886903429403901e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0002630425442475826</v>
+        <v>8.596947009209543e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.071199221769348e-06</v>
+        <v>7.141538662835956e-05</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.000147396931424737</v>
+        <v>8.19928536657244e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0004203035787213594</v>
+        <v>6.294809281826019e-06</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.272783265449107e-07</v>
+        <v>2.662086808413733e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>5.869686356163584e-05</v>
+        <v>0.0002563426387496293</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.0001869678089860827</v>
+        <v>5.349902858142741e-05</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0001216217497130856</v>
+        <v>5.788661383121507e-06</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0003040529845748097</v>
+        <v>0.0001630011538509279</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0001011249842122197</v>
+        <v>4.977645585313439e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.0001102113528759219</v>
+        <v>4.116570926271379e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0001172870543086901</v>
+        <v>0.0001050522405421361</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.552703078137711e-05</v>
+        <v>6.157653115224093e-05</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0001465415698476136</v>
+        <v>0.0001709316566120833</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.76758902752772e-05</v>
+        <v>7.318967982428148e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>4.530306614469737e-05</v>
+        <v>6.467541970778257e-05</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.996063292608596e-05</v>
+        <v>3.379715508344816e-06</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0006246178527362645</v>
+        <v>0.0001829753018682823</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.472930307500064e-05</v>
+        <v>5.887424413231201e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>8.236928260885179e-05</v>
+        <v>6.441757432185113e-05</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.60163721779827e-05</v>
+        <v>0.0001023498334689066</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0001063782401615754</v>
+        <v>0.0001748388167470694</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.431875954149291e-05</v>
+        <v>4.776771675096825e-05</v>
       </c>
       <c r="CB16" t="n">
-        <v>7.064495730446652e-05</v>
+        <v>5.531170609174296e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0001199721591547132</v>
+        <v>2.537008913350292e-05</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.37017338804435e-05</v>
+        <v>6.735672286595218e-06</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0002411451132502407</v>
+        <v>7.512206502724439e-05</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.994231519754976e-05</v>
+        <v>2.664120620465837e-05</v>
       </c>
       <c r="CG16" t="n">
-        <v>4.340078157838434e-05</v>
+        <v>3.894970723195001e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>5.572563168243505e-05</v>
+        <v>8.525281737092882e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>9.413728548679501e-05</v>
+        <v>0.0001151683463831432</v>
       </c>
       <c r="CJ16" t="n">
-        <v>9.027821943163872e-05</v>
+        <v>4.283075759303756e-05</v>
       </c>
       <c r="CK16" t="n">
-        <v>2.891020812967326e-06</v>
+        <v>1.580420575919561e-05</v>
       </c>
       <c r="CL16" t="n">
-        <v>3.252904934925027e-05</v>
+        <v>3.593971632653847e-05</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0003743809647858143</v>
+        <v>3.806550012086518e-06</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0002397179923718795</v>
+        <v>0.0001825658546295017</v>
       </c>
       <c r="CO16" t="n">
-        <v>6.216447218321264e-05</v>
+        <v>0.0001367686199955642</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0003700689412653446</v>
+        <v>0.0002065510052489117</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0001069603094947524</v>
+        <v>6.493579712696373e-05</v>
       </c>
       <c r="CR16" t="n">
-        <v>8.142924343701452e-05</v>
+        <v>4.958812496624887e-05</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.000198571608052589</v>
+        <v>2.725679587456398e-05</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0002899517130572349</v>
+        <v>0.0001435492013115436</v>
       </c>
       <c r="CU16" t="n">
-        <v>3.741211912711151e-05</v>
+        <v>3.359138281666674e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.502071947674267e-05</v>
+        <v>1.642038478166796e-05</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.000206134922336787</v>
+        <v>7.085653487592936e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>3.500977618386969e-05</v>
+        <v>2.888335802708752e-05</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0001082533708540723</v>
+        <v>6.09017770329956e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.958461067872122e-05</v>
+        <v>7.752338569844142e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>6.889667565701529e-05</v>
+        <v>0.000137472030473873</v>
       </c>
       <c r="DB16" t="n">
-        <v>8.774825982982293e-05</v>
+        <v>1.74225806404138e-05</v>
       </c>
       <c r="DC16" t="n">
-        <v>5.676104046870023e-05</v>
+        <v>1.064080606738571e-05</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.599529686151072e-06</v>
+        <v>1.214465646626195e-05</v>
       </c>
       <c r="DE16" t="n">
-        <v>3.740864849532954e-05</v>
+        <v>1.756360506988131e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0002316227037226781</v>
+        <v>0.0001733531826175749</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.909305840148591e-05</v>
+        <v>7.472444849554449e-05</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0002416142087895423</v>
+        <v>1.812920163501985e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.000380815239623189</v>
+        <v>0.0001408277312293649</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0003470592782832682</v>
+        <v>0.0001327218924416229</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.751732871634886e-05</v>
+        <v>4.625829024007544e-05</v>
       </c>
       <c r="DL16" t="n">
-        <v>9.781880362424999e-05</v>
+        <v>4.342473403085023e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0003054027329199016</v>
+        <v>2.044057873717975e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>5.577705087489448e-05</v>
+        <v>2.932072857220192e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>8.433853508904576e-05</v>
+        <v>1.754897311911918e-06</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0001782328763511032</v>
+        <v>4.327045462559909e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>2.101619793393183e-05</v>
+        <v>5.22018235642463e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>2.562943700468168e-05</v>
+        <v>4.06539547839202e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>2.991149813169613e-05</v>
+        <v>1.722751221677754e-05</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.000231745361816138</v>
+        <v>7.62856361689046e-05</v>
       </c>
       <c r="DU16" t="n">
-        <v>2.985868741234299e-05</v>
+        <v>0.0001264232123503461</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.0001043134907376952</v>
+        <v>1.467346373829059e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>7.583787373732775e-05</v>
+        <v>1.775515738700051e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0001728483766783029</v>
+        <v>5.535821401281282e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0001218558099935763</v>
+        <v>6.393293006112799e-07</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0001393405982526019</v>
+        <v>0.00011908017040696</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0001753268879838288</v>
+        <v>5.529661848413525e-06</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.649946509336587e-05</v>
+        <v>3.40309452440124e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.783618947432842e-05</v>
+        <v>8.992499715532176e-06</v>
       </c>
       <c r="ED16" t="n">
-        <v>9.537135338177904e-05</v>
+        <v>0.0001026364843710326</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0001443779183318838</v>
+        <v>0.0001804046332836151</v>
       </c>
       <c r="EF16" t="n">
-        <v>3.257816570112482e-05</v>
+        <v>3.304526762804016e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0002851857279893011</v>
+        <v>5.146280454937369e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>6.827378456364386e-06</v>
+        <v>1.097782660508528e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>1.40335614560172e-05</v>
+        <v>2.31280064326711e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>3.204101085430011e-05</v>
+        <v>4.552409882307984e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>1.037844776874408e-05</v>
+        <v>0.0001232013019034639</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0001023038348648697</v>
+        <v>5.561062425840646e-05</v>
       </c>
       <c r="EM16" t="n">
-        <v>8.813582826405764e-05</v>
+        <v>2.1403691789601e-05</v>
       </c>
       <c r="EN16" t="n">
-        <v>4.381749386084266e-05</v>
+        <v>3.312876742711524e-06</v>
       </c>
       <c r="EO16" t="n">
-        <v>7.866730447858572e-05</v>
+        <v>3.672317325253971e-05</v>
       </c>
       <c r="EP16" t="n">
-        <v>6.176826718728989e-05</v>
+        <v>7.585213461425155e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>5.438490916276351e-05</v>
+        <v>9.26462234929204e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>8.931293996283785e-05</v>
+        <v>3.385061427252367e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>6.040312291588634e-05</v>
+        <v>5.64530782867223e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0001464099332224578</v>
+        <v>8.84130276972428e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0002262975904159248</v>
+        <v>4.459995398065075e-05</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0002353776653762907</v>
+        <v>8.467352017760277e-06</v>
       </c>
       <c r="EW16" t="n">
-        <v>1.068264828063548e-05</v>
+        <v>3.931586252292618e-05</v>
       </c>
       <c r="EX16" t="n">
-        <v>3.089781603193842e-05</v>
+        <v>2.29590768867638e-05</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.000215436695725657</v>
+        <v>0.0001093862811103463</v>
       </c>
       <c r="EZ16" t="n">
-        <v>8.540715498384088e-06</v>
+        <v>1.636584056541324e-05</v>
       </c>
       <c r="FA16" t="n">
-        <v>6.364122782542836e-06</v>
+        <v>7.380897295661271e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>1.040840015775757e-05</v>
+        <v>7.481115608243272e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>8.776437607593834e-05</v>
+        <v>0.0001185068394988775</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0001358969311695546</v>
+        <v>4.456383976503275e-05</v>
       </c>
       <c r="FE16" t="n">
-        <v>9.136474545812234e-06</v>
+        <v>4.874709702562541e-08</v>
       </c>
       <c r="FF16" t="n">
-        <v>5.873571717529558e-05</v>
+        <v>3.837697477138136e-06</v>
       </c>
       <c r="FG16" t="n">
-        <v>3.23895292240195e-05</v>
+        <v>6.580762601515744e-06</v>
       </c>
       <c r="FH16" t="n">
-        <v>9.418024274054915e-05</v>
+        <v>0.0001353945408482105</v>
       </c>
       <c r="FI16" t="n">
-        <v>3.938126610592008e-06</v>
+        <v>7.748184725642204e-05</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.000138080125907436</v>
+        <v>2.502687493688427e-05</v>
       </c>
       <c r="FK16" t="n">
-        <v>3.374952211743221e-05</v>
+        <v>0.0001142540131695569</v>
       </c>
       <c r="FL16" t="n">
-        <v>4.739545693155378e-05</v>
+        <v>0.000101417004771065</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0001460894709452987</v>
+        <v>9.779450192581862e-05</v>
       </c>
       <c r="FN16" t="n">
-        <v>1.402810084982775e-05</v>
+        <v>4.904130037175491e-05</v>
       </c>
       <c r="FO16" t="n">
-        <v>5.791188596049324e-05</v>
+        <v>0.0001827458472689614</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.000146779915667139</v>
+        <v>3.990299956058152e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0002677395823411644</v>
+        <v>6.942402251297608e-05</v>
       </c>
       <c r="FR16" t="n">
-        <v>8.363074448425323e-05</v>
+        <v>0.0001322724128840491</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.0001176818477688357</v>
+        <v>0.000118050396849867</v>
       </c>
       <c r="FT16" t="n">
-        <v>7.024089427432045e-06</v>
+        <v>0.0002351481816731393</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0001435456506442279</v>
+        <v>1.116719067795202e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0001602158881723881</v>
+        <v>4.26960650656838e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>1.497214361734223e-05</v>
+        <v>0.0002769799903035164</v>
       </c>
       <c r="FX16" t="n">
-        <v>1.210026493936311e-05</v>
+        <v>7.839812315069139e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0002173978864448145</v>
+        <v>5.965675518382341e-05</v>
       </c>
       <c r="FZ16" t="n">
-        <v>1.940096626640297e-05</v>
+        <v>8.191935921786353e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>2.728773324633949e-05</v>
+        <v>0.0001325746561633423</v>
       </c>
       <c r="GB16" t="n">
-        <v>2.798049899865873e-05</v>
+        <v>2.341005529160611e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.0001389385579386726</v>
+        <v>0.0001417827152181417</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0001644201402086765</v>
+        <v>0.0001752156240399927</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0001909704005811363</v>
+        <v>9.199089254252613e-05</v>
       </c>
       <c r="GF16" t="n">
-        <v>5.719038745155558e-05</v>
+        <v>5.784836503153201e-06</v>
       </c>
       <c r="GG16" t="n">
-        <v>3.400946297915652e-05</v>
+        <v>4.259658089722507e-05</v>
       </c>
     </row>
   </sheetData>
